--- a/Weekly Reports/Weekly Sales Report (main).xlsx
+++ b/Weekly Reports/Weekly Sales Report (main).xlsx
@@ -2686,7 +2686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA161"/>
+  <dimension ref="A1:AA162"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.44140625" customWidth="1" style="68" min="1" max="1"/>
@@ -7680,16 +7680,32 @@
       <c r="AA147" s="402" t="n"/>
     </row>
     <row r="148" ht="27.6" customHeight="1">
-      <c r="A148" s="403" t="n"/>
+      <c r="A148" s="403" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B148" s="347" t="n"/>
       <c r="C148" s="404" t="n"/>
-      <c r="D148" s="323" t="n"/>
-      <c r="E148" s="402" t="n"/>
-      <c r="F148" s="402" t="n"/>
-      <c r="G148" s="402" t="n"/>
-      <c r="H148" s="402" t="n"/>
-      <c r="I148" s="402" t="n"/>
-      <c r="J148" s="405" t="n"/>
+      <c r="D148" s="323" t="n">
+        <v>309</v>
+      </c>
+      <c r="E148" s="402" t="n">
+        <v>18841.12</v>
+      </c>
+      <c r="F148" s="402" t="n">
+        <v>16017.92</v>
+      </c>
+      <c r="G148" s="402" t="n">
+        <v>109.16</v>
+      </c>
+      <c r="H148" s="402" t="n">
+        <v>604.27</v>
+      </c>
+      <c r="I148" s="402" t="n">
+        <v>2109.77</v>
+      </c>
+      <c r="J148" s="338" t="n"/>
       <c r="K148" s="405" t="n"/>
       <c r="L148" s="406" t="n"/>
       <c r="M148" s="402" t="n"/>
@@ -7709,42 +7725,46 @@
       <c r="AA148" s="402" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="45" t="inlineStr">
+      <c r="A149" s="403" t="n"/>
+      <c r="B149" s="347" t="n"/>
+      <c r="C149" s="404" t="n"/>
+      <c r="D149" s="323" t="n"/>
+      <c r="E149" s="402" t="n"/>
+      <c r="F149" s="402" t="n"/>
+      <c r="G149" s="402" t="n"/>
+      <c r="H149" s="402" t="n"/>
+      <c r="I149" s="402" t="n"/>
+      <c r="J149" s="338" t="n"/>
+      <c r="K149" s="405" t="n"/>
+      <c r="L149" s="406" t="n"/>
+      <c r="M149" s="402" t="n"/>
+      <c r="N149" s="398" t="n"/>
+      <c r="O149" s="398" t="n"/>
+      <c r="P149" s="402" t="n"/>
+      <c r="Q149" s="402" t="n"/>
+      <c r="R149" s="402" t="n"/>
+      <c r="S149" s="402" t="n"/>
+      <c r="T149" s="402" t="n"/>
+      <c r="U149" s="402" t="n"/>
+      <c r="V149" s="402" t="n"/>
+      <c r="W149" s="402" t="n"/>
+      <c r="X149" s="402" t="n"/>
+      <c r="Y149" s="402" t="n"/>
+      <c r="Z149" s="402" t="n"/>
+      <c r="AA149" s="402" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="45" t="inlineStr">
         <is>
           <t>Karachi Highway Karahi</t>
         </is>
       </c>
-      <c r="B149" s="358" t="n"/>
-      <c r="C149" s="355" t="n"/>
-      <c r="D149" s="45" t="n"/>
-      <c r="E149" s="45" t="n"/>
-      <c r="F149" s="398" t="n"/>
-      <c r="G149" s="45" t="n"/>
-      <c r="H149" s="45" t="n"/>
-      <c r="I149" s="45" t="n"/>
-      <c r="J149" s="45" t="n"/>
-      <c r="K149" s="398" t="n"/>
-      <c r="L149" s="398" t="n"/>
-      <c r="M149" s="398" t="n"/>
-      <c r="N149" s="45" t="n"/>
-      <c r="O149" s="45" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="30" t="inlineStr">
-        <is>
-          <t>Statement For Selected Period</t>
-        </is>
-      </c>
-      <c r="B150" s="45" t="n"/>
-      <c r="C150" s="30" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="D150" s="30" t="n"/>
-      <c r="E150" s="30" t="n"/>
+      <c r="B150" s="358" t="n"/>
+      <c r="C150" s="355" t="n"/>
+      <c r="D150" s="45" t="n"/>
+      <c r="E150" s="45" t="n"/>
       <c r="F150" s="398" t="n"/>
-      <c r="G150" s="398" t="n"/>
+      <c r="G150" s="45" t="n"/>
       <c r="H150" s="45" t="n"/>
       <c r="I150" s="45" t="n"/>
       <c r="J150" s="45" t="n"/>
@@ -7755,37 +7775,39 @@
       <c r="O150" s="45" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
-        </is>
-      </c>
-      <c r="B151" s="56" t="n"/>
-      <c r="C151" s="398" t="n">
-        <v>21368.16</v>
-      </c>
-      <c r="D151" s="56" t="n"/>
-      <c r="E151" s="56" t="n"/>
-      <c r="F151" s="382" t="n"/>
-      <c r="G151" s="56" t="n"/>
-      <c r="H151" s="56" t="n"/>
-      <c r="I151" s="56" t="n"/>
-      <c r="J151" s="56" t="n"/>
-      <c r="K151" s="56" t="n"/>
-      <c r="L151" s="56" t="n"/>
-      <c r="M151" s="56" t="n"/>
-      <c r="N151" s="56" t="n"/>
-      <c r="O151" s="56" t="n"/>
+      <c r="A151" s="30" t="inlineStr">
+        <is>
+          <t>Statement For Selected Period</t>
+        </is>
+      </c>
+      <c r="B151" s="45" t="n"/>
+      <c r="C151" s="30" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="D151" s="30" t="n"/>
+      <c r="E151" s="30" t="n"/>
+      <c r="F151" s="398" t="n"/>
+      <c r="G151" s="398" t="n"/>
+      <c r="H151" s="45" t="n"/>
+      <c r="I151" s="45" t="n"/>
+      <c r="J151" s="45" t="n"/>
+      <c r="K151" s="398" t="n"/>
+      <c r="L151" s="398" t="n"/>
+      <c r="M151" s="398" t="n"/>
+      <c r="N151" s="45" t="n"/>
+      <c r="O151" s="45" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B152" s="56" t="n"/>
       <c r="C152" s="398" t="n">
-        <v>24661.29</v>
+        <v>21368.16</v>
       </c>
       <c r="D152" s="56" t="n"/>
       <c r="E152" s="56" t="n"/>
@@ -7803,12 +7825,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B153" s="56" t="n"/>
-      <c r="C153" s="56" t="n">
-        <v>11848.11</v>
+      <c r="C153" s="398" t="n">
+        <v>24661.29</v>
       </c>
       <c r="D153" s="56" t="n"/>
       <c r="E153" s="56" t="n"/>
@@ -7826,12 +7848,12 @@
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>Mar 30 - Apr 05 2026</t>
+          <t>Mar 23 - Mar 29 2026</t>
         </is>
       </c>
       <c r="B154" s="56" t="n"/>
-      <c r="C154" s="398" t="n">
-        <v>12740.16</v>
+      <c r="C154" s="56" t="n">
+        <v>11848.11</v>
       </c>
       <c r="D154" s="56" t="n"/>
       <c r="E154" s="56" t="n"/>
@@ -7847,79 +7869,102 @@
       <c r="O154" s="56" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>Mar 30 - Apr 05 2026</t>
+        </is>
+      </c>
+      <c r="B155" s="56" t="n"/>
+      <c r="C155" s="398" t="n">
+        <v>12740.16</v>
+      </c>
+      <c r="D155" s="56" t="n"/>
+      <c r="E155" s="56" t="n"/>
+      <c r="F155" s="382" t="n"/>
+      <c r="G155" s="56" t="n"/>
+      <c r="H155" s="56" t="n"/>
+      <c r="I155" s="56" t="n"/>
+      <c r="J155" s="56" t="n"/>
+      <c r="K155" s="56" t="n"/>
+      <c r="L155" s="56" t="n"/>
+      <c r="M155" s="56" t="n"/>
+      <c r="N155" s="56" t="n"/>
+      <c r="O155" s="56" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Apr 06 - Apr 12</t>
-        </is>
-      </c>
-      <c r="B155" s="45" t="n"/>
-      <c r="C155" s="398" t="n">
-        <v>11206.32</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="11" t="inlineStr">
-        <is>
-          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B156" s="45" t="n"/>
       <c r="C156" s="398" t="n">
-        <v>11891.16</v>
+        <v>11206.32</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>Apr 20 - Apr 26</t>
+          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B157" s="45" t="n"/>
       <c r="C157" s="398" t="n">
-        <v>11986.83</v>
+        <v>11891.16</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="399" t="inlineStr">
-        <is>
-          <t>Apr 27 - May 03</t>
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>Apr 20 - Apr 26</t>
         </is>
       </c>
       <c r="B158" s="45" t="n"/>
       <c r="C158" s="398" t="n">
-        <v>11275.7</v>
+        <v>11986.83</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="399" t="inlineStr">
         <is>
-          <t>May 4 - May 10</t>
+          <t>Apr 27 - May 03</t>
         </is>
       </c>
       <c r="B159" s="45" t="n"/>
       <c r="C159" s="398" t="n">
+        <v>11275.7</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="399" t="inlineStr">
+        <is>
+          <t>May 4 - May 10</t>
+        </is>
+      </c>
+      <c r="B160" s="45" t="n"/>
+      <c r="C160" s="398" t="n">
         <v>12649.28</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="403" t="inlineStr">
-        <is>
-          <t>May 11 - May 17</t>
-        </is>
-      </c>
-      <c r="B160" s="347" t="n"/>
-      <c r="C160" s="404" t="n">
-        <v>15271.56</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="403" t="inlineStr">
         <is>
-          <t>May 18 - May 24</t>
+          <t>May 11 - May 17</t>
         </is>
       </c>
       <c r="B161" s="347" t="n"/>
       <c r="C161" s="404" t="n">
+        <v>15271.56</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="403" t="inlineStr">
+        <is>
+          <t>May 18 - May 24</t>
+        </is>
+      </c>
+      <c r="B162" s="347" t="n"/>
+      <c r="C162" s="404" t="n">
         <v>13083.73</v>
       </c>
     </row>
@@ -7940,7 +7985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="28.109375" customWidth="1" min="1" max="1"/>
@@ -10833,16 +10878,32 @@
       <c r="AC58" s="323" t="n"/>
     </row>
     <row r="59" ht="27.6" customHeight="1">
-      <c r="A59" s="353" t="n"/>
+      <c r="A59" s="353" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B59" s="353" t="n"/>
       <c r="C59" s="399" t="n"/>
       <c r="D59" s="399" t="n"/>
-      <c r="E59" s="323" t="n"/>
-      <c r="F59" s="323" t="n"/>
-      <c r="G59" s="323" t="n"/>
-      <c r="H59" s="323" t="n"/>
-      <c r="I59" s="323" t="n"/>
-      <c r="J59" s="323" t="n"/>
+      <c r="E59" s="323" t="n">
+        <v>435</v>
+      </c>
+      <c r="F59" s="323" t="n">
+        <v>13171.28</v>
+      </c>
+      <c r="G59" s="323" t="n">
+        <v>8276.540000000001</v>
+      </c>
+      <c r="H59" s="323" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="323" t="n">
+        <v>221.07</v>
+      </c>
+      <c r="J59" s="323" t="n">
+        <v>4673.67</v>
+      </c>
       <c r="K59" s="406" t="n"/>
       <c r="L59" s="406" t="n"/>
       <c r="M59" s="473" t="n"/>
@@ -10864,52 +10925,48 @@
       <c r="AC59" s="323" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="399" t="inlineStr">
+      <c r="A60" s="353" t="n"/>
+      <c r="B60" s="353" t="n"/>
+      <c r="C60" s="399" t="n"/>
+      <c r="D60" s="399" t="n"/>
+      <c r="E60" s="323" t="n"/>
+      <c r="F60" s="323" t="n"/>
+      <c r="G60" s="323" t="n"/>
+      <c r="H60" s="323" t="n"/>
+      <c r="I60" s="323" t="n"/>
+      <c r="J60" s="323" t="n"/>
+      <c r="K60" s="406" t="n"/>
+      <c r="L60" s="406" t="n"/>
+      <c r="M60" s="473" t="n"/>
+      <c r="N60" s="473" t="n"/>
+      <c r="O60" s="323" t="n"/>
+      <c r="P60" s="323" t="n"/>
+      <c r="Q60" s="323" t="n"/>
+      <c r="R60" s="323" t="n"/>
+      <c r="S60" s="323" t="n"/>
+      <c r="T60" s="323" t="n"/>
+      <c r="U60" s="323" t="n"/>
+      <c r="V60" s="323" t="n"/>
+      <c r="W60" s="323" t="n"/>
+      <c r="X60" s="323" t="n"/>
+      <c r="Y60" s="323" t="n"/>
+      <c r="Z60" s="323" t="n"/>
+      <c r="AA60" s="323" t="n"/>
+      <c r="AB60" s="323" t="n"/>
+      <c r="AC60" s="323" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="399" t="inlineStr">
         <is>
           <t>Queen KKW</t>
         </is>
       </c>
-      <c r="B60" s="358" t="n"/>
-      <c r="C60" s="358" t="n"/>
-      <c r="D60" s="355" t="n"/>
-      <c r="E60" s="399" t="n"/>
-      <c r="F60" s="399" t="n"/>
-      <c r="G60" s="382" t="n"/>
-      <c r="H60" s="382" t="n"/>
-      <c r="I60" s="382" t="n"/>
-      <c r="J60" s="382" t="n"/>
-      <c r="K60" s="382" t="n"/>
-      <c r="L60" s="382" t="n"/>
-      <c r="M60" s="382" t="n"/>
-      <c r="N60" s="382" t="n"/>
-      <c r="O60" s="382" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="479" t="inlineStr">
-        <is>
-          <t>Statement For Selected Period</t>
-        </is>
-      </c>
-      <c r="B61" s="479" t="inlineStr">
-        <is>
-          <t>Total Revenue (Net Sales)</t>
-        </is>
-      </c>
-      <c r="C61" s="479" t="inlineStr">
-        <is>
-          <t>Royalties
-(6%) +HST</t>
-        </is>
-      </c>
-      <c r="D61" s="479" t="inlineStr">
-        <is>
-          <t>Marketing
-(2%) +HST</t>
-        </is>
-      </c>
-      <c r="E61" s="479" t="n"/>
-      <c r="F61" s="479" t="n"/>
-      <c r="G61" s="389" t="n"/>
+      <c r="B61" s="358" t="n"/>
+      <c r="C61" s="358" t="n"/>
+      <c r="D61" s="355" t="n"/>
+      <c r="E61" s="399" t="n"/>
+      <c r="F61" s="399" t="n"/>
+      <c r="G61" s="382" t="n"/>
       <c r="H61" s="382" t="n"/>
       <c r="I61" s="382" t="n"/>
       <c r="J61" s="382" t="n"/>
@@ -10920,49 +10977,55 @@
       <c r="O61" s="382" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="n">
-        <v>9469.559999999999</v>
-      </c>
-      <c r="C62" s="399">
-        <f>(B57*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D62" s="399">
-        <f>(B57*0.02)*1.13</f>
-        <v/>
-      </c>
-      <c r="E62" s="56" t="n"/>
-      <c r="F62" s="56" t="n"/>
-      <c r="G62" s="56" t="n"/>
-      <c r="H62" s="56" t="n"/>
-      <c r="I62" s="56" t="n"/>
-      <c r="J62" s="56" t="n"/>
-      <c r="K62" s="56" t="n"/>
-      <c r="L62" s="56" t="n"/>
-      <c r="M62" s="56" t="n"/>
-      <c r="N62" s="56" t="n"/>
-      <c r="O62" s="56" t="n"/>
+      <c r="A62" s="479" t="inlineStr">
+        <is>
+          <t>Statement For Selected Period</t>
+        </is>
+      </c>
+      <c r="B62" s="479" t="inlineStr">
+        <is>
+          <t>Total Revenue (Net Sales)</t>
+        </is>
+      </c>
+      <c r="C62" s="479" t="inlineStr">
+        <is>
+          <t>Royalties
+(6%) +HST</t>
+        </is>
+      </c>
+      <c r="D62" s="479" t="inlineStr">
+        <is>
+          <t>Marketing
+(2%) +HST</t>
+        </is>
+      </c>
+      <c r="E62" s="479" t="n"/>
+      <c r="F62" s="479" t="n"/>
+      <c r="G62" s="389" t="n"/>
+      <c r="H62" s="382" t="n"/>
+      <c r="I62" s="382" t="n"/>
+      <c r="J62" s="382" t="n"/>
+      <c r="K62" s="382" t="n"/>
+      <c r="L62" s="382" t="n"/>
+      <c r="M62" s="382" t="n"/>
+      <c r="N62" s="382" t="n"/>
+      <c r="O62" s="382" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
-        <v>10550.93</v>
+        <v>9469.559999999999</v>
       </c>
       <c r="C63" s="399">
-        <f>(B58*0.06)*1.13</f>
+        <f>(B57*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D63" s="399">
-        <f>(B58*0.02)*1.13</f>
+        <f>(B57*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E63" s="56" t="n"/>
@@ -10980,18 +11043,18 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
-        <v>8077.93</v>
+        <v>10550.93</v>
       </c>
       <c r="C64" s="399">
-        <f>(B59*0.06)*1.13</f>
+        <f>(B58*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D64" s="399">
-        <f>(B59*0.02)*1.13</f>
+        <f>(B58*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E64" s="56" t="n"/>
@@ -11009,18 +11072,18 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>Mar 30 - Apr 05 2026</t>
+          <t>Mar 23 - Mar 29 2026</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
-        <v>10135.13</v>
+        <v>8077.93</v>
       </c>
       <c r="C65" s="399">
-        <f>(B60*0.06)*1.13</f>
+        <f>(B59*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D65" s="399">
-        <f>(B60*0.02)*1.13</f>
+        <f>(B59*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E65" s="56" t="n"/>
@@ -11036,127 +11099,156 @@
       <c r="O65" s="56" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Mar 30 - Apr 05 2026</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>10135.13</v>
+      </c>
+      <c r="C66" s="399">
+        <f>(B60*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D66" s="399">
+        <f>(B60*0.02)*1.13</f>
+        <v/>
+      </c>
+      <c r="E66" s="56" t="n"/>
+      <c r="F66" s="56" t="n"/>
+      <c r="G66" s="56" t="n"/>
+      <c r="H66" s="56" t="n"/>
+      <c r="I66" s="56" t="n"/>
+      <c r="J66" s="56" t="n"/>
+      <c r="K66" s="56" t="n"/>
+      <c r="L66" s="56" t="n"/>
+      <c r="M66" s="56" t="n"/>
+      <c r="N66" s="56" t="n"/>
+      <c r="O66" s="56" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Apr 06 - Apr 12</t>
         </is>
       </c>
-      <c r="B66" s="11" t="n">
+      <c r="B67" s="11" t="n">
         <v>9562.98</v>
       </c>
-      <c r="C66" s="399">
+      <c r="C67" s="399">
         <f>(B61*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D66" s="399">
+      <c r="D67" s="399">
         <f>(B61*0.02)*1.13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>Apr 13 - Apr 19</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="n">
-        <v>8161.77</v>
-      </c>
-      <c r="C67" s="399">
-        <f>(B62*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D67" s="399">
-        <f>(B62*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>Apr 20 - Apr 26</t>
+          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>9410.119999999999</v>
+        <v>8161.77</v>
       </c>
       <c r="C68" s="399">
-        <f>(B63*0.06)*1.13</f>
+        <f>(B62*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D68" s="399">
-        <f>(B63*0.02)*1.13</f>
+        <f>(B62*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
+          <t>Apr 20 - Apr 26</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>9410.119999999999</v>
+      </c>
+      <c r="C69" s="399">
+        <f>(B63*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D69" s="399">
+        <f>(B63*0.02)*1.13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
           <t>Apr 27 - May 03</t>
         </is>
       </c>
-      <c r="B69" s="11" t="n">
+      <c r="B70" s="11" t="n">
         <v>10362.14</v>
       </c>
-      <c r="C69" s="399">
+      <c r="C70" s="399">
         <f>(B65*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D69" s="399">
+      <c r="D70" s="399">
         <f>(B65*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="334" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="334" t="inlineStr">
         <is>
           <t>May 4 - May 10</t>
         </is>
       </c>
-      <c r="B70" s="334" t="n">
+      <c r="B71" s="334" t="n">
         <v>10059.3</v>
       </c>
-      <c r="C70" s="399">
+      <c r="C71" s="399">
         <f>(B66*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D70" s="399">
+      <c r="D71" s="399">
         <f>(B66*0.02)*1.13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="353" t="inlineStr">
-        <is>
-          <t>May 11 - May 17</t>
-        </is>
-      </c>
-      <c r="B71" s="353" t="n">
-        <v>9437.639999999999</v>
-      </c>
-      <c r="C71" s="399">
-        <f>(B68*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D71" s="399">
-        <f>(B68*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="353" t="inlineStr">
         <is>
+          <t>May 11 - May 17</t>
+        </is>
+      </c>
+      <c r="B72" s="353" t="n">
+        <v>9437.639999999999</v>
+      </c>
+      <c r="C72" s="399">
+        <f>(B68*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D72" s="399">
+        <f>(B68*0.02)*1.13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="353" t="inlineStr">
+        <is>
           <t>May 18 - May 24</t>
         </is>
       </c>
-      <c r="B72" s="353" t="n">
+      <c r="B73" s="353" t="n">
         <v>9840.34</v>
       </c>
-      <c r="C72" s="399">
+      <c r="C73" s="399">
         <f>(B70*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D72" s="399">
+      <c r="D73" s="399">
         <f>(B70*0.02)*1.13</f>
         <v/>
       </c>
@@ -11175,7 +11267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD82"/>
+  <dimension ref="A1:AD83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col width="26.44140625" customWidth="1" style="560" min="1" max="1"/>
@@ -15040,16 +15132,32 @@
       <c r="AD68" s="402" t="n"/>
     </row>
     <row r="69" ht="27.6" customHeight="1">
-      <c r="A69" s="353" t="n"/>
+      <c r="A69" s="353" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B69" s="471" t="n"/>
       <c r="C69" s="471" t="n"/>
       <c r="D69" s="471" t="n"/>
-      <c r="E69" s="402" t="n"/>
-      <c r="F69" s="402" t="n"/>
-      <c r="G69" s="402" t="n"/>
-      <c r="H69" s="402" t="n"/>
-      <c r="I69" s="402" t="n"/>
-      <c r="J69" s="402" t="n"/>
+      <c r="E69" s="402" t="n">
+        <v>428</v>
+      </c>
+      <c r="F69" s="402" t="n">
+        <v>12986.95</v>
+      </c>
+      <c r="G69" s="402" t="n">
+        <v>9346.610000000001</v>
+      </c>
+      <c r="H69" s="402" t="n">
+        <v>118.77</v>
+      </c>
+      <c r="I69" s="402" t="n">
+        <v>401.43</v>
+      </c>
+      <c r="J69" s="402" t="n">
+        <v>3120.14</v>
+      </c>
       <c r="K69" s="405" t="n"/>
       <c r="L69" s="402" t="n"/>
       <c r="M69" s="402" t="n"/>
@@ -15072,53 +15180,48 @@
       <c r="AD69" s="402" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="546" t="inlineStr">
+      <c r="A70" s="353" t="n"/>
+      <c r="B70" s="471" t="n"/>
+      <c r="C70" s="471" t="n"/>
+      <c r="D70" s="471" t="n"/>
+      <c r="E70" s="402" t="n"/>
+      <c r="F70" s="402" t="n"/>
+      <c r="G70" s="402" t="n"/>
+      <c r="H70" s="402" t="n"/>
+      <c r="I70" s="402" t="n"/>
+      <c r="J70" s="402" t="n"/>
+      <c r="K70" s="405" t="n"/>
+      <c r="L70" s="402" t="n"/>
+      <c r="M70" s="402" t="n"/>
+      <c r="N70" s="402" t="n"/>
+      <c r="O70" s="471" t="n"/>
+      <c r="P70" s="471" t="n"/>
+      <c r="Q70" s="402" t="n"/>
+      <c r="R70" s="402" t="n"/>
+      <c r="S70" s="402" t="n"/>
+      <c r="T70" s="402" t="n"/>
+      <c r="U70" s="402" t="n"/>
+      <c r="V70" s="402" t="n"/>
+      <c r="W70" s="402" t="n"/>
+      <c r="X70" s="402" t="n"/>
+      <c r="Y70" s="402" t="n"/>
+      <c r="Z70" s="402" t="n"/>
+      <c r="AA70" s="402" t="n"/>
+      <c r="AB70" s="402" t="n"/>
+      <c r="AC70" s="402" t="n"/>
+      <c r="AD70" s="402" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="546" t="inlineStr">
         <is>
           <t>Lebovic</t>
         </is>
       </c>
-      <c r="B70" s="358" t="n"/>
-      <c r="C70" s="358" t="n"/>
-      <c r="D70" s="355" t="n"/>
-      <c r="E70" s="546" t="n"/>
-      <c r="F70" s="546" t="n"/>
-      <c r="G70" s="394" t="n"/>
-      <c r="H70" s="394" t="n"/>
-      <c r="I70" s="394" t="n"/>
-      <c r="J70" s="394" t="n"/>
-      <c r="K70" s="394" t="n"/>
-      <c r="L70" s="394" t="n"/>
-      <c r="M70" s="394" t="n"/>
-      <c r="N70" s="394" t="n"/>
-      <c r="O70" s="394" t="n"/>
-      <c r="P70" s="394" t="n"/>
-      <c r="Q70" s="394" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="415" t="inlineStr">
-        <is>
-          <t>Statement For Selected Period</t>
-        </is>
-      </c>
-      <c r="B71" s="415" t="inlineStr">
-        <is>
-          <t>Total Revenue (Net Sales)</t>
-        </is>
-      </c>
-      <c r="C71" s="415" t="inlineStr">
-        <is>
-          <t>Royalties
-(6%) +HST</t>
-        </is>
-      </c>
-      <c r="D71" s="415" t="inlineStr">
-        <is>
-          <t>Marketing
-(2%) +HST</t>
-        </is>
-      </c>
-      <c r="E71" s="415" t="n"/>
-      <c r="F71" s="415" t="n"/>
+      <c r="B71" s="358" t="n"/>
+      <c r="C71" s="358" t="n"/>
+      <c r="D71" s="355" t="n"/>
+      <c r="E71" s="546" t="n"/>
+      <c r="F71" s="546" t="n"/>
       <c r="G71" s="394" t="n"/>
       <c r="H71" s="394" t="n"/>
       <c r="I71" s="394" t="n"/>
@@ -15132,51 +15235,57 @@
       <c r="Q71" s="394" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
-        </is>
-      </c>
-      <c r="B72" s="394" t="n">
-        <v>10028.44</v>
-      </c>
-      <c r="C72" s="394">
-        <f>(B67*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D72" s="394">
-        <f>(B67*0.02)*1.13</f>
-        <v/>
-      </c>
-      <c r="E72" s="382" t="n"/>
-      <c r="F72" s="382" t="n"/>
-      <c r="G72" s="382" t="n"/>
-      <c r="H72" s="382" t="n"/>
-      <c r="I72" s="382" t="n"/>
-      <c r="J72" s="382" t="n"/>
-      <c r="K72" s="382" t="n"/>
-      <c r="L72" s="382" t="n"/>
-      <c r="M72" s="382" t="n"/>
-      <c r="N72" s="382" t="n"/>
-      <c r="O72" s="382" t="n"/>
-      <c r="P72" s="382" t="n"/>
-      <c r="Q72" s="382" t="n"/>
+      <c r="A72" s="415" t="inlineStr">
+        <is>
+          <t>Statement For Selected Period</t>
+        </is>
+      </c>
+      <c r="B72" s="415" t="inlineStr">
+        <is>
+          <t>Total Revenue (Net Sales)</t>
+        </is>
+      </c>
+      <c r="C72" s="415" t="inlineStr">
+        <is>
+          <t>Royalties
+(6%) +HST</t>
+        </is>
+      </c>
+      <c r="D72" s="415" t="inlineStr">
+        <is>
+          <t>Marketing
+(2%) +HST</t>
+        </is>
+      </c>
+      <c r="E72" s="415" t="n"/>
+      <c r="F72" s="415" t="n"/>
+      <c r="G72" s="394" t="n"/>
+      <c r="H72" s="394" t="n"/>
+      <c r="I72" s="394" t="n"/>
+      <c r="J72" s="394" t="n"/>
+      <c r="K72" s="394" t="n"/>
+      <c r="L72" s="394" t="n"/>
+      <c r="M72" s="394" t="n"/>
+      <c r="N72" s="394" t="n"/>
+      <c r="O72" s="394" t="n"/>
+      <c r="P72" s="394" t="n"/>
+      <c r="Q72" s="394" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B73" s="394" t="n">
-        <v>14607.41</v>
+        <v>10028.44</v>
       </c>
       <c r="C73" s="394">
-        <f>(B68*0.06)*1.13</f>
+        <f>(B67*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D73" s="394">
-        <f>(B68*0.02)*1.13</f>
+        <f>(B67*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E73" s="382" t="n"/>
@@ -15196,18 +15305,18 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B74" s="394" t="n">
-        <v>11031.85</v>
+        <v>14607.41</v>
       </c>
       <c r="C74" s="394">
-        <f>(B69*0.06)*1.13</f>
+        <f>(B68*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D74" s="394">
-        <f>(B69*0.02)*1.13</f>
+        <f>(B68*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E74" s="382" t="n"/>
@@ -15227,143 +15336,174 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
+          <t>Mar 23 - Mar 29 2026</t>
+        </is>
+      </c>
+      <c r="B75" s="394" t="n">
+        <v>11031.85</v>
+      </c>
+      <c r="C75" s="394">
+        <f>(B69*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D75" s="394">
+        <f>(B69*0.02)*1.13</f>
+        <v/>
+      </c>
+      <c r="E75" s="382" t="n"/>
+      <c r="F75" s="382" t="n"/>
+      <c r="G75" s="382" t="n"/>
+      <c r="H75" s="382" t="n"/>
+      <c r="I75" s="382" t="n"/>
+      <c r="J75" s="382" t="n"/>
+      <c r="K75" s="382" t="n"/>
+      <c r="L75" s="382" t="n"/>
+      <c r="M75" s="382" t="n"/>
+      <c r="N75" s="382" t="n"/>
+      <c r="O75" s="382" t="n"/>
+      <c r="P75" s="382" t="n"/>
+      <c r="Q75" s="382" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
           <t>Mar 30 - Apr 05 2026</t>
         </is>
       </c>
-      <c r="B75" s="394" t="n">
+      <c r="B76" s="394" t="n">
         <v>12357.04</v>
       </c>
-      <c r="C75" s="394">
+      <c r="C76" s="394">
         <f>(B70*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D75" s="394">
+      <c r="D76" s="394">
         <f>(B70*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Apr 06 - Apr 12</t>
         </is>
       </c>
-      <c r="B76" s="394" t="n">
+      <c r="B77" s="394" t="n">
         <v>11773.82</v>
       </c>
-      <c r="C76" s="394">
+      <c r="C77" s="394">
         <f>(B71*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D76" s="394">
+      <c r="D77" s="394">
         <f>(B71*0.02)*1.13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>Apr 13 - Apr 19</t>
-        </is>
-      </c>
-      <c r="B77" s="394" t="n">
-        <v>11156.76</v>
-      </c>
-      <c r="C77" s="394">
-        <f>(B72*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D77" s="394">
-        <f>(B72*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>Apr 20 - Apr 26</t>
+          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B78" s="394" t="n">
-        <v>11058.33</v>
+        <v>11156.76</v>
       </c>
       <c r="C78" s="394">
-        <f>(B73*0.06)*1.13</f>
+        <f>(B72*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D78" s="394">
-        <f>(B73*0.02)*1.13</f>
+        <f>(B72*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
+          <t>Apr 20 - Apr 26</t>
+        </is>
+      </c>
+      <c r="B79" s="394" t="n">
+        <v>11058.33</v>
+      </c>
+      <c r="C79" s="394">
+        <f>(B73*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D79" s="394">
+        <f>(B73*0.02)*1.13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
           <t>Apr 27 - May 03</t>
         </is>
       </c>
-      <c r="B79" s="394" t="n">
+      <c r="B80" s="394" t="n">
         <v>10850.57</v>
       </c>
-      <c r="C79" s="394">
+      <c r="C80" s="394">
         <f>(B75*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D79" s="394">
+      <c r="D80" s="394">
         <f>(B75*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="334" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="334" t="inlineStr">
         <is>
           <t>May 4 - May 10</t>
         </is>
       </c>
-      <c r="B80" s="471" t="n">
+      <c r="B81" s="471" t="n">
         <v>10497.02</v>
       </c>
-      <c r="C80" s="394">
+      <c r="C81" s="394">
         <f>(B76*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D80" s="394">
+      <c r="D81" s="394">
         <f>(B76*0.02)*1.13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="353" t="inlineStr">
-        <is>
-          <t>May 11 - May 17</t>
-        </is>
-      </c>
-      <c r="B81" s="471" t="n">
-        <v>11914.85</v>
-      </c>
-      <c r="C81" s="394">
-        <f>(B78*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D81" s="394">
-        <f>(B78*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="353" t="inlineStr">
         <is>
+          <t>May 11 - May 17</t>
+        </is>
+      </c>
+      <c r="B82" s="471" t="n">
+        <v>11914.85</v>
+      </c>
+      <c r="C82" s="394">
+        <f>(B78*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D82" s="394">
+        <f>(B78*0.02)*1.13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="353" t="inlineStr">
+        <is>
           <t>May 18 - May 24</t>
         </is>
       </c>
-      <c r="B82" s="471" t="n">
+      <c r="B83" s="471" t="n">
         <v>9788.68</v>
       </c>
-      <c r="C82" s="394">
+      <c r="C83" s="394">
         <f>(B80*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D82" s="394">
+      <c r="D83" s="394">
         <f>(B80*0.02)*1.13</f>
         <v/>
       </c>
@@ -17016,7 +17156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA161"/>
+  <dimension ref="A1:AA162"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="17.4"/>
   <cols>
     <col width="31.109375" customWidth="1" style="407" min="1" max="1"/>
@@ -21624,15 +21764,31 @@
       <c r="AA147" s="402" t="n"/>
     </row>
     <row r="148" ht="14.4" customHeight="1">
-      <c r="A148" s="403" t="n"/>
+      <c r="A148" s="403" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B148" s="403" t="n"/>
       <c r="C148" s="452" t="n"/>
-      <c r="D148" s="323" t="n"/>
-      <c r="E148" s="402" t="n"/>
-      <c r="F148" s="402" t="n"/>
-      <c r="G148" s="402" t="n"/>
-      <c r="H148" s="402" t="n"/>
-      <c r="I148" s="402" t="n"/>
+      <c r="D148" s="323" t="n">
+        <v>455</v>
+      </c>
+      <c r="E148" s="402" t="n">
+        <v>19078.48</v>
+      </c>
+      <c r="F148" s="402" t="n">
+        <v>16351.38</v>
+      </c>
+      <c r="G148" s="402" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="H148" s="402" t="n">
+        <v>242.19</v>
+      </c>
+      <c r="I148" s="402" t="n">
+        <v>2421.19</v>
+      </c>
       <c r="J148" s="406" t="n"/>
       <c r="K148" s="406" t="n"/>
       <c r="L148" s="402" t="n"/>
@@ -21653,43 +21809,48 @@
       <c r="AA148" s="402" t="n"/>
     </row>
     <row r="149" ht="14.4" customHeight="1">
-      <c r="A149" s="453" t="inlineStr">
+      <c r="A149" s="403" t="n"/>
+      <c r="B149" s="403" t="n"/>
+      <c r="C149" s="452" t="n"/>
+      <c r="D149" s="323" t="n"/>
+      <c r="E149" s="402" t="n"/>
+      <c r="F149" s="402" t="n"/>
+      <c r="G149" s="402" t="n"/>
+      <c r="H149" s="402" t="n"/>
+      <c r="I149" s="402" t="n"/>
+      <c r="J149" s="406" t="n"/>
+      <c r="K149" s="406" t="n"/>
+      <c r="L149" s="402" t="n"/>
+      <c r="M149" s="402" t="n"/>
+      <c r="N149" s="399" t="n"/>
+      <c r="O149" s="402" t="n"/>
+      <c r="P149" s="402" t="n"/>
+      <c r="Q149" s="402" t="n"/>
+      <c r="R149" s="402" t="n"/>
+      <c r="S149" s="402" t="n"/>
+      <c r="T149" s="402" t="n"/>
+      <c r="U149" s="402" t="n"/>
+      <c r="V149" s="402" t="n"/>
+      <c r="W149" s="402" t="n"/>
+      <c r="X149" s="402" t="n"/>
+      <c r="Y149" s="402" t="n"/>
+      <c r="Z149" s="402" t="n"/>
+      <c r="AA149" s="402" t="n"/>
+    </row>
+    <row r="150" ht="14.4" customHeight="1">
+      <c r="A150" s="453" t="inlineStr">
         <is>
           <t>Karachi Kababwala</t>
         </is>
       </c>
-      <c r="B149" s="358" t="n"/>
-      <c r="C149" s="355" t="n"/>
-      <c r="D149" s="453" t="n"/>
-      <c r="E149" s="453" t="n"/>
-      <c r="F149" s="45" t="n"/>
-      <c r="G149" s="45" t="n"/>
-      <c r="H149" s="45" t="n"/>
-      <c r="I149" s="30" t="n"/>
-      <c r="J149" s="399" t="n"/>
-      <c r="K149" s="399" t="n"/>
-      <c r="L149" s="399" t="n"/>
-      <c r="M149" s="399" t="n"/>
-      <c r="N149" s="399" t="n"/>
-    </row>
-    <row r="150" ht="14.4" customHeight="1">
-      <c r="A150" s="454" t="inlineStr">
-        <is>
-          <t>Statement For Selected Period</t>
-        </is>
-      </c>
-      <c r="B150" s="399" t="n"/>
-      <c r="C150" s="454" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="D150" s="454" t="n"/>
-      <c r="E150" s="454" t="n"/>
-      <c r="F150" s="399" t="n"/>
-      <c r="G150" s="399" t="n"/>
-      <c r="H150" s="399" t="n"/>
-      <c r="I150" s="399" t="n"/>
+      <c r="B150" s="358" t="n"/>
+      <c r="C150" s="355" t="n"/>
+      <c r="D150" s="453" t="n"/>
+      <c r="E150" s="453" t="n"/>
+      <c r="F150" s="45" t="n"/>
+      <c r="G150" s="45" t="n"/>
+      <c r="H150" s="45" t="n"/>
+      <c r="I150" s="30" t="n"/>
       <c r="J150" s="399" t="n"/>
       <c r="K150" s="399" t="n"/>
       <c r="L150" s="399" t="n"/>
@@ -21697,36 +21858,38 @@
       <c r="N150" s="399" t="n"/>
     </row>
     <row r="151" ht="14.4" customHeight="1">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
-        </is>
-      </c>
-      <c r="B151" s="382" t="n"/>
-      <c r="C151" s="382" t="n">
-        <v>12151.46</v>
-      </c>
-      <c r="D151" s="382" t="n"/>
-      <c r="E151" s="382" t="n"/>
-      <c r="F151" s="382" t="n"/>
-      <c r="G151" s="382" t="n"/>
-      <c r="H151" s="382" t="n"/>
-      <c r="I151" s="382" t="n"/>
-      <c r="J151" s="382" t="n"/>
-      <c r="K151" s="382" t="n"/>
-      <c r="L151" s="382" t="n"/>
-      <c r="M151" s="382" t="n"/>
-      <c r="N151" s="382" t="n"/>
+      <c r="A151" s="454" t="inlineStr">
+        <is>
+          <t>Statement For Selected Period</t>
+        </is>
+      </c>
+      <c r="B151" s="399" t="n"/>
+      <c r="C151" s="454" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="D151" s="454" t="n"/>
+      <c r="E151" s="454" t="n"/>
+      <c r="F151" s="399" t="n"/>
+      <c r="G151" s="399" t="n"/>
+      <c r="H151" s="399" t="n"/>
+      <c r="I151" s="399" t="n"/>
+      <c r="J151" s="399" t="n"/>
+      <c r="K151" s="399" t="n"/>
+      <c r="L151" s="399" t="n"/>
+      <c r="M151" s="399" t="n"/>
+      <c r="N151" s="399" t="n"/>
     </row>
     <row r="152" ht="14.4" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B152" s="382" t="n"/>
-      <c r="C152" s="449" t="n">
-        <v>24770.57</v>
+      <c r="C152" s="382" t="n">
+        <v>12151.46</v>
       </c>
       <c r="D152" s="382" t="n"/>
       <c r="E152" s="382" t="n"/>
@@ -21743,12 +21906,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B153" s="382" t="n"/>
-      <c r="C153" s="382" t="n">
-        <v>14955.6</v>
+      <c r="C153" s="449" t="n">
+        <v>24770.57</v>
       </c>
       <c r="D153" s="382" t="n"/>
       <c r="E153" s="382" t="n"/>
@@ -21765,12 +21928,12 @@
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>Mar 30 - Apr 05 2026</t>
+          <t>Mar 23 - Mar 29 2026</t>
         </is>
       </c>
       <c r="B154" s="382" t="n"/>
-      <c r="C154" s="449" t="n">
-        <v>16935.81</v>
+      <c r="C154" s="382" t="n">
+        <v>14955.6</v>
       </c>
       <c r="D154" s="382" t="n"/>
       <c r="E154" s="382" t="n"/>
@@ -21785,79 +21948,101 @@
       <c r="N154" s="382" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>Apr 06 - Apr 12</t>
-        </is>
-      </c>
-      <c r="B155" s="399" t="n"/>
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>Mar 30 - Apr 05 2026</t>
+        </is>
+      </c>
+      <c r="B155" s="382" t="n"/>
       <c r="C155" s="449" t="n">
-        <v>15482.39</v>
-      </c>
+        <v>16935.81</v>
+      </c>
+      <c r="D155" s="382" t="n"/>
+      <c r="E155" s="382" t="n"/>
+      <c r="F155" s="382" t="n"/>
+      <c r="G155" s="382" t="n"/>
+      <c r="H155" s="382" t="n"/>
+      <c r="I155" s="382" t="n"/>
+      <c r="J155" s="382" t="n"/>
+      <c r="K155" s="382" t="n"/>
+      <c r="L155" s="382" t="n"/>
+      <c r="M155" s="382" t="n"/>
+      <c r="N155" s="382" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Apr 13 - Apr 19</t>
+          <t>Apr 06 - Apr 12</t>
         </is>
       </c>
       <c r="B156" s="399" t="n"/>
       <c r="C156" s="449" t="n">
-        <v>16004.83</v>
+        <v>15482.39</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Apr 20 - Apr 26</t>
+          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B157" s="399" t="n"/>
       <c r="C157" s="449" t="n">
-        <v>14512.87</v>
+        <v>16004.83</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Apr 27 - May 03</t>
+          <t>Apr 20 - Apr 26</t>
         </is>
       </c>
       <c r="B158" s="399" t="n"/>
       <c r="C158" s="449" t="n">
-        <v>15776.71</v>
+        <v>14512.87</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>May 4 - May 10</t>
+          <t>Apr 27 - May 03</t>
         </is>
       </c>
       <c r="B159" s="399" t="n"/>
       <c r="C159" s="449" t="n">
-        <v>16708.87</v>
+        <v>15776.71</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>May 11 - May 17</t>
+          <t>May 4 - May 10</t>
         </is>
       </c>
       <c r="B160" s="399" t="n"/>
       <c r="C160" s="449" t="n">
-        <v>16279.46</v>
+        <v>16708.87</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>May 18 - May 24</t>
+          <t>May 11 - May 17</t>
         </is>
       </c>
       <c r="B161" s="399" t="n"/>
       <c r="C161" s="449" t="n">
+        <v>16279.46</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>May 18 - May 24</t>
+        </is>
+      </c>
+      <c r="B162" s="399" t="n"/>
+      <c r="C162" s="449" t="n">
         <v>15628.16</v>
       </c>
     </row>
@@ -21877,7 +22062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P161"/>
+  <dimension ref="A1:P162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.109375" customWidth="1" min="1" max="1"/>
@@ -26772,63 +26957,70 @@
       </c>
     </row>
     <row r="147" ht="27.6" customHeight="1">
-      <c r="A147" s="474" t="n"/>
+      <c r="A147" s="474" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B147" s="474" t="n"/>
       <c r="C147" s="474" t="n"/>
-      <c r="D147" s="302" t="n"/>
-      <c r="E147" s="2" t="n"/>
-      <c r="F147" s="329" t="n"/>
-      <c r="G147" s="472" t="n"/>
-      <c r="H147" s="118" t="n"/>
-      <c r="I147" s="118" t="n"/>
+      <c r="D147" s="302" t="n">
+        <v>623</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>22735.22</v>
+      </c>
+      <c r="F147" s="329" t="n">
+        <v>16325.45</v>
+      </c>
+      <c r="G147" s="472" t="n">
+        <v>158.66</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>6251.11</v>
+      </c>
       <c r="J147" s="405" t="n"/>
       <c r="K147" s="343" t="n"/>
       <c r="L147" s="343" t="n"/>
       <c r="M147" s="343" t="n"/>
       <c r="N147" s="473" t="n"/>
       <c r="O147" s="473" t="n"/>
-      <c r="P147" s="186" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="382" t="inlineStr">
+      <c r="A148" s="474" t="n"/>
+      <c r="B148" s="474" t="n"/>
+      <c r="C148" s="474" t="n"/>
+      <c r="D148" s="302" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="329" t="n"/>
+      <c r="G148" s="472" t="n"/>
+      <c r="H148" s="118" t="n"/>
+      <c r="I148" s="118" t="n"/>
+      <c r="J148" s="405" t="n"/>
+      <c r="K148" s="343" t="n"/>
+      <c r="L148" s="343" t="n"/>
+      <c r="M148" s="343" t="n"/>
+      <c r="N148" s="473" t="n"/>
+      <c r="O148" s="473" t="n"/>
+      <c r="P148" s="186" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="382" t="inlineStr">
         <is>
           <t>Pizza K Heartland</t>
         </is>
       </c>
-      <c r="B148" s="358" t="n"/>
-      <c r="C148" s="355" t="n"/>
-      <c r="D148" s="382" t="n"/>
-      <c r="E148" s="382" t="n"/>
-      <c r="F148" s="118" t="n"/>
-      <c r="G148" s="382" t="n"/>
-      <c r="H148" s="382" t="n"/>
-      <c r="I148" s="11" t="n"/>
-      <c r="J148" s="382" t="n"/>
-      <c r="K148" s="382" t="n"/>
-      <c r="L148" s="382" t="n"/>
-      <c r="M148" s="382" t="n"/>
-      <c r="N148" s="382" t="n"/>
-      <c r="O148" s="382" t="n"/>
-      <c r="P148" s="186" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="418" t="inlineStr">
-        <is>
-          <t>Statement For Selected Period</t>
-        </is>
-      </c>
-      <c r="B149" s="382" t="n"/>
-      <c r="C149" s="420" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="D149" s="420" t="n"/>
-      <c r="E149" s="420" t="n"/>
-      <c r="F149" s="389" t="n"/>
+      <c r="B149" s="358" t="n"/>
+      <c r="C149" s="355" t="n"/>
+      <c r="D149" s="382" t="n"/>
+      <c r="E149" s="382" t="n"/>
+      <c r="F149" s="118" t="n"/>
       <c r="G149" s="382" t="n"/>
       <c r="H149" s="382" t="n"/>
-      <c r="I149" s="382" t="n"/>
+      <c r="I149" s="11" t="n"/>
       <c r="J149" s="382" t="n"/>
       <c r="K149" s="382" t="n"/>
       <c r="L149" s="382" t="n"/>
@@ -26838,18 +27030,20 @@
       <c r="P149" s="186" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
+      <c r="A150" s="418" t="inlineStr">
+        <is>
+          <t>Statement For Selected Period</t>
         </is>
       </c>
       <c r="B150" s="382" t="n"/>
-      <c r="C150" s="394" t="n">
-        <v>19160.79</v>
-      </c>
-      <c r="D150" s="394" t="n"/>
-      <c r="E150" s="394" t="n"/>
-      <c r="F150" s="382" t="n"/>
+      <c r="C150" s="420" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="D150" s="420" t="n"/>
+      <c r="E150" s="420" t="n"/>
+      <c r="F150" s="389" t="n"/>
       <c r="G150" s="382" t="n"/>
       <c r="H150" s="382" t="n"/>
       <c r="I150" s="382" t="n"/>
@@ -26859,16 +27053,17 @@
       <c r="M150" s="382" t="n"/>
       <c r="N150" s="382" t="n"/>
       <c r="O150" s="382" t="n"/>
+      <c r="P150" s="186" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B151" s="382" t="n"/>
       <c r="C151" s="394" t="n">
-        <v>25373.5</v>
+        <v>19160.79</v>
       </c>
       <c r="D151" s="394" t="n"/>
       <c r="E151" s="394" t="n"/>
@@ -26886,12 +27081,12 @@
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B152" s="382" t="n"/>
       <c r="C152" s="394" t="n">
-        <v>18256.37</v>
+        <v>25373.5</v>
       </c>
       <c r="D152" s="394" t="n"/>
       <c r="E152" s="394" t="n"/>
@@ -26909,12 +27104,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>Mar 30 - Apr 05 2026</t>
+          <t>Mar 23 - Mar 29 2026</t>
         </is>
       </c>
       <c r="B153" s="382" t="n"/>
       <c r="C153" s="394" t="n">
-        <v>19869.5</v>
+        <v>18256.37</v>
       </c>
       <c r="D153" s="394" t="n"/>
       <c r="E153" s="394" t="n"/>
@@ -26930,14 +27125,14 @@
       <c r="O153" s="382" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Apr 06 - Apr 12</t>
-        </is>
-      </c>
-      <c r="B154" s="394" t="n"/>
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>Mar 30 - Apr 05 2026</t>
+        </is>
+      </c>
+      <c r="B154" s="382" t="n"/>
       <c r="C154" s="394" t="n">
-        <v>18326.65</v>
+        <v>19869.5</v>
       </c>
       <c r="D154" s="394" t="n"/>
       <c r="E154" s="394" t="n"/>
@@ -26953,14 +27148,14 @@
       <c r="O154" s="382" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="11" t="inlineStr">
-        <is>
-          <t>Apr 13 - Apr 19</t>
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Apr 06 - Apr 12</t>
         </is>
       </c>
       <c r="B155" s="394" t="n"/>
       <c r="C155" s="394" t="n">
-        <v>19074.55</v>
+        <v>18326.65</v>
       </c>
       <c r="D155" s="394" t="n"/>
       <c r="E155" s="394" t="n"/>
@@ -26978,12 +27173,12 @@
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>Apr 20 - Apr 26</t>
+          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B156" s="394" t="n"/>
       <c r="C156" s="394" t="n">
-        <v>20029.68</v>
+        <v>19074.55</v>
       </c>
       <c r="D156" s="394" t="n"/>
       <c r="E156" s="394" t="n"/>
@@ -26999,14 +27194,14 @@
       <c r="O156" s="382" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="394" t="inlineStr">
-        <is>
-          <t>Apr 27 - May 03</t>
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>Apr 20 - Apr 26</t>
         </is>
       </c>
       <c r="B157" s="394" t="n"/>
       <c r="C157" s="394" t="n">
-        <v>18234.87</v>
+        <v>20029.68</v>
       </c>
       <c r="D157" s="394" t="n"/>
       <c r="E157" s="394" t="n"/>
@@ -27022,14 +27217,14 @@
       <c r="O157" s="382" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="471" t="inlineStr">
-        <is>
-          <t>May 4 - May 10</t>
-        </is>
-      </c>
-      <c r="B158" s="471" t="n"/>
-      <c r="C158" s="471" t="n">
-        <v>17712.87</v>
+      <c r="A158" s="394" t="inlineStr">
+        <is>
+          <t>Apr 27 - May 03</t>
+        </is>
+      </c>
+      <c r="B158" s="394" t="n"/>
+      <c r="C158" s="394" t="n">
+        <v>18234.87</v>
       </c>
       <c r="D158" s="394" t="n"/>
       <c r="E158" s="394" t="n"/>
@@ -27045,14 +27240,14 @@
       <c r="O158" s="382" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="474" t="inlineStr">
-        <is>
-          <t>May 11 - May 17</t>
-        </is>
-      </c>
-      <c r="B159" s="474" t="n"/>
-      <c r="C159" s="474" t="n">
-        <v>19413.89</v>
+      <c r="A159" s="471" t="inlineStr">
+        <is>
+          <t>May 4 - May 10</t>
+        </is>
+      </c>
+      <c r="B159" s="471" t="n"/>
+      <c r="C159" s="471" t="n">
+        <v>17712.87</v>
       </c>
       <c r="D159" s="394" t="n"/>
       <c r="E159" s="394" t="n"/>
@@ -27070,12 +27265,12 @@
     <row r="160">
       <c r="A160" s="474" t="inlineStr">
         <is>
-          <t>May 18 - May 24</t>
+          <t>May 11 - May 17</t>
         </is>
       </c>
       <c r="B160" s="474" t="n"/>
       <c r="C160" s="474" t="n">
-        <v>18448.88</v>
+        <v>19413.89</v>
       </c>
       <c r="D160" s="394" t="n"/>
       <c r="E160" s="394" t="n"/>
@@ -27091,9 +27286,15 @@
       <c r="O160" s="382" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="382" t="n"/>
-      <c r="B161" s="382" t="n"/>
-      <c r="C161" s="394" t="n"/>
+      <c r="A161" s="474" t="inlineStr">
+        <is>
+          <t>May 18 - May 24</t>
+        </is>
+      </c>
+      <c r="B161" s="474" t="n"/>
+      <c r="C161" s="474" t="n">
+        <v>18448.88</v>
+      </c>
       <c r="D161" s="394" t="n"/>
       <c r="E161" s="394" t="n"/>
       <c r="F161" s="382" t="n"/>
@@ -27106,6 +27307,23 @@
       <c r="M161" s="382" t="n"/>
       <c r="N161" s="382" t="n"/>
       <c r="O161" s="382" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="382" t="n"/>
+      <c r="B162" s="382" t="n"/>
+      <c r="C162" s="394" t="n"/>
+      <c r="D162" s="394" t="n"/>
+      <c r="E162" s="394" t="n"/>
+      <c r="F162" s="382" t="n"/>
+      <c r="G162" s="382" t="n"/>
+      <c r="H162" s="382" t="n"/>
+      <c r="I162" s="382" t="n"/>
+      <c r="J162" s="382" t="n"/>
+      <c r="K162" s="382" t="n"/>
+      <c r="L162" s="382" t="n"/>
+      <c r="M162" s="382" t="n"/>
+      <c r="N162" s="382" t="n"/>
+      <c r="O162" s="382" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -27123,7 +27341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z174"/>
+  <dimension ref="A1:Z175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="39.33203125" customWidth="1" min="1" max="1"/>
@@ -31629,15 +31847,31 @@
       <c r="Z160" s="401" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="474" t="n"/>
+      <c r="A161" s="474" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B161" s="478" t="n"/>
       <c r="C161" s="474" t="n"/>
-      <c r="D161" s="319" t="n"/>
-      <c r="E161" s="401" t="n"/>
-      <c r="F161" s="401" t="n"/>
-      <c r="G161" s="401" t="n"/>
-      <c r="H161" s="401" t="n"/>
-      <c r="I161" s="401" t="n"/>
+      <c r="D161" s="319" t="n">
+        <v>1221</v>
+      </c>
+      <c r="E161" s="401" t="n">
+        <v>43345.83</v>
+      </c>
+      <c r="F161" s="401" t="n">
+        <v>30668.64</v>
+      </c>
+      <c r="G161" s="401" t="n">
+        <v>458.86</v>
+      </c>
+      <c r="H161" s="401" t="n">
+        <v>784.15</v>
+      </c>
+      <c r="I161" s="401" t="n">
+        <v>11434.18</v>
+      </c>
       <c r="J161" s="406" t="n"/>
       <c r="K161" s="401" t="n"/>
       <c r="L161" s="473" t="n"/>
@@ -31657,77 +31891,84 @@
       <c r="Z161" s="401" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="453" t="inlineStr">
+      <c r="A162" s="474" t="n"/>
+      <c r="B162" s="478" t="n"/>
+      <c r="C162" s="474" t="n"/>
+      <c r="D162" s="319" t="n"/>
+      <c r="E162" s="401" t="n"/>
+      <c r="F162" s="401" t="n"/>
+      <c r="G162" s="401" t="n"/>
+      <c r="H162" s="401" t="n"/>
+      <c r="I162" s="401" t="n"/>
+      <c r="J162" s="406" t="n"/>
+      <c r="K162" s="401" t="n"/>
+      <c r="L162" s="473" t="n"/>
+      <c r="M162" s="473" t="n"/>
+      <c r="N162" s="401" t="n"/>
+      <c r="O162" s="401" t="n"/>
+      <c r="P162" s="401" t="n"/>
+      <c r="Q162" s="401" t="n"/>
+      <c r="R162" s="401" t="n"/>
+      <c r="S162" s="401" t="n"/>
+      <c r="T162" s="401" t="n"/>
+      <c r="U162" s="401" t="n"/>
+      <c r="V162" s="401" t="n"/>
+      <c r="W162" s="401" t="n"/>
+      <c r="X162" s="401" t="n"/>
+      <c r="Y162" s="401" t="n"/>
+      <c r="Z162" s="401" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="453" t="inlineStr">
         <is>
           <t>Pizza K Eglinton</t>
         </is>
       </c>
-      <c r="B162" s="358" t="n"/>
-      <c r="C162" s="355" t="n"/>
-      <c r="D162" s="453" t="n"/>
-      <c r="E162" s="453" t="n"/>
-      <c r="F162" s="118" t="n"/>
-      <c r="G162" s="118" t="n"/>
-      <c r="H162" s="11" t="n"/>
-      <c r="I162" s="118" t="n"/>
-      <c r="J162" s="382" t="n"/>
-      <c r="K162" s="382" t="n"/>
-      <c r="L162" s="382" t="n"/>
-      <c r="M162" s="382" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="454" t="inlineStr">
+      <c r="B163" s="358" t="n"/>
+      <c r="C163" s="355" t="n"/>
+      <c r="D163" s="453" t="n"/>
+      <c r="E163" s="453" t="n"/>
+      <c r="F163" s="118" t="n"/>
+      <c r="G163" s="118" t="n"/>
+      <c r="H163" s="11" t="n"/>
+      <c r="I163" s="118" t="n"/>
+      <c r="J163" s="382" t="n"/>
+      <c r="K163" s="382" t="n"/>
+      <c r="L163" s="382" t="n"/>
+      <c r="M163" s="382" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="454" t="inlineStr">
         <is>
           <t>Statement For Selected Period</t>
         </is>
       </c>
-      <c r="B163" s="479" t="n"/>
-      <c r="C163" s="454" t="inlineStr">
+      <c r="B164" s="479" t="n"/>
+      <c r="C164" s="454" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="D163" s="454" t="n"/>
-      <c r="E163" s="454" t="n"/>
-      <c r="F163" s="480" t="n"/>
-      <c r="G163" s="480" t="n"/>
-      <c r="H163" s="480" t="n"/>
-      <c r="I163" s="480" t="n"/>
-      <c r="J163" s="480" t="n"/>
-      <c r="K163" s="480" t="n"/>
-      <c r="L163" s="480" t="n"/>
-      <c r="M163" s="480" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
-        </is>
-      </c>
-      <c r="B164" s="56" t="n"/>
-      <c r="C164" s="394" t="n">
-        <v>36636.96</v>
-      </c>
-      <c r="D164" s="118" t="n"/>
-      <c r="E164" s="118" t="n"/>
-      <c r="F164" s="56" t="n"/>
-      <c r="G164" s="56" t="n"/>
-      <c r="H164" s="56" t="n"/>
-      <c r="I164" s="56" t="n"/>
-      <c r="J164" s="56" t="n"/>
-      <c r="K164" s="56" t="n"/>
-      <c r="L164" s="56" t="n"/>
-      <c r="M164" s="56" t="n"/>
+      <c r="D164" s="454" t="n"/>
+      <c r="E164" s="454" t="n"/>
+      <c r="F164" s="480" t="n"/>
+      <c r="G164" s="480" t="n"/>
+      <c r="H164" s="480" t="n"/>
+      <c r="I164" s="480" t="n"/>
+      <c r="J164" s="480" t="n"/>
+      <c r="K164" s="480" t="n"/>
+      <c r="L164" s="480" t="n"/>
+      <c r="M164" s="480" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B165" s="56" t="n"/>
       <c r="C165" s="394" t="n">
-        <v>53093.71</v>
+        <v>36636.96</v>
       </c>
       <c r="D165" s="118" t="n"/>
       <c r="E165" s="118" t="n"/>
@@ -31743,12 +31984,12 @@
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B166" s="56" t="n"/>
-      <c r="C166" s="118" t="n">
-        <v>37080.2</v>
+      <c r="C166" s="394" t="n">
+        <v>53093.71</v>
       </c>
       <c r="D166" s="118" t="n"/>
       <c r="E166" s="118" t="n"/>
@@ -31764,12 +32005,12 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>Mar 30 - Apr 05 2026</t>
+          <t>Mar 23 - Mar 29 2026</t>
         </is>
       </c>
       <c r="B167" s="56" t="n"/>
-      <c r="C167" s="394" t="n">
-        <v>43302.97</v>
+      <c r="C167" s="118" t="n">
+        <v>37080.2</v>
       </c>
       <c r="D167" s="118" t="n"/>
       <c r="E167" s="118" t="n"/>
@@ -31783,79 +32024,100 @@
       <c r="M167" s="56" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>Mar 30 - Apr 05 2026</t>
+        </is>
+      </c>
+      <c r="B168" s="56" t="n"/>
+      <c r="C168" s="394" t="n">
+        <v>43302.97</v>
+      </c>
+      <c r="D168" s="118" t="n"/>
+      <c r="E168" s="118" t="n"/>
+      <c r="F168" s="56" t="n"/>
+      <c r="G168" s="56" t="n"/>
+      <c r="H168" s="56" t="n"/>
+      <c r="I168" s="56" t="n"/>
+      <c r="J168" s="56" t="n"/>
+      <c r="K168" s="56" t="n"/>
+      <c r="L168" s="56" t="n"/>
+      <c r="M168" s="56" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Apr 06 - Apr 12</t>
-        </is>
-      </c>
-      <c r="B168" s="382" t="n"/>
-      <c r="C168" s="394" t="n">
-        <v>33902.39</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="11" t="inlineStr">
-        <is>
-          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B169" s="382" t="n"/>
       <c r="C169" s="394" t="n">
-        <v>35877.6</v>
+        <v>33902.39</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>Apr 20 - Apr 26</t>
+          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B170" s="382" t="n"/>
       <c r="C170" s="394" t="n">
-        <v>36765.17</v>
+        <v>35877.6</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="394" t="inlineStr">
-        <is>
-          <t>Apr 27 - May 03</t>
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>Apr 20 - Apr 26</t>
         </is>
       </c>
       <c r="B171" s="382" t="n"/>
       <c r="C171" s="394" t="n">
+        <v>36765.17</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="394" t="inlineStr">
+        <is>
+          <t>Apr 27 - May 03</t>
+        </is>
+      </c>
+      <c r="B172" s="382" t="n"/>
+      <c r="C172" s="394" t="n">
         <v>35937.92</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="471" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="471" t="inlineStr">
         <is>
           <t>May 4 - May 10</t>
         </is>
       </c>
-      <c r="B172" s="473" t="n"/>
-      <c r="C172" s="471" t="n">
+      <c r="B173" s="473" t="n"/>
+      <c r="C173" s="471" t="n">
         <v>37355.96</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="474" t="inlineStr">
-        <is>
-          <t>May 11 - May 17</t>
-        </is>
-      </c>
-      <c r="B173" s="478" t="n"/>
-      <c r="C173" s="474" t="n">
-        <v>35974.85000000001</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="474" t="inlineStr">
         <is>
-          <t>May 18 - May 24</t>
+          <t>May 11 - May 17</t>
         </is>
       </c>
       <c r="B174" s="478" t="n"/>
       <c r="C174" s="474" t="n">
+        <v>35974.85000000001</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="474" t="inlineStr">
+        <is>
+          <t>May 18 - May 24</t>
+        </is>
+      </c>
+      <c r="B175" s="478" t="n"/>
+      <c r="C175" s="474" t="n">
         <v>38082.75</v>
       </c>
     </row>
@@ -31875,7 +32137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R160"/>
+  <dimension ref="A1:R161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="37.33203125" customWidth="1" min="1" max="1"/>
@@ -36686,15 +36948,31 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="474" t="n"/>
+      <c r="A147" s="474" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B147" s="474" t="n"/>
       <c r="C147" s="474" t="n"/>
-      <c r="D147" s="2" t="n"/>
-      <c r="E147" s="2" t="n"/>
-      <c r="F147" s="332" t="n"/>
-      <c r="G147" s="472" t="n"/>
-      <c r="H147" s="448" t="n"/>
-      <c r="I147" s="448" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>1857</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>74782.62</v>
+      </c>
+      <c r="F147" s="332" t="n">
+        <v>69197.60000000001</v>
+      </c>
+      <c r="G147" s="472" t="n">
+        <v>112.28</v>
+      </c>
+      <c r="H147" s="448" t="n">
+        <v>907.77</v>
+      </c>
+      <c r="I147" s="448" t="n">
+        <v>4564.97</v>
+      </c>
       <c r="J147" s="405" t="n"/>
       <c r="K147" s="448" t="n"/>
       <c r="L147" s="332" t="n"/>
@@ -36705,46 +36983,38 @@
       <c r="Q147" s="471" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="394" t="inlineStr">
+      <c r="A148" s="474" t="n"/>
+      <c r="B148" s="474" t="n"/>
+      <c r="C148" s="474" t="n"/>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="332" t="n"/>
+      <c r="G148" s="472" t="n"/>
+      <c r="H148" s="448" t="n"/>
+      <c r="I148" s="448" t="n"/>
+      <c r="J148" s="405" t="n"/>
+      <c r="K148" s="448" t="n"/>
+      <c r="L148" s="332" t="n"/>
+      <c r="M148" s="512" t="n"/>
+      <c r="N148" s="513" t="n"/>
+      <c r="O148" s="513" t="n"/>
+      <c r="P148" s="471" t="n"/>
+      <c r="Q148" s="471" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="394" t="inlineStr">
         <is>
           <t>Karachi Food Court</t>
         </is>
       </c>
-      <c r="B148" s="358" t="n"/>
-      <c r="C148" s="355" t="n"/>
-      <c r="D148" s="394" t="n"/>
-      <c r="E148" s="394" t="n"/>
-      <c r="F148" s="118" t="n"/>
-      <c r="G148" s="118" t="n"/>
-      <c r="H148" s="394" t="n"/>
-      <c r="I148" s="11" t="n"/>
-      <c r="J148" s="394" t="n"/>
-      <c r="K148" s="394" t="n"/>
-      <c r="L148" s="394" t="n"/>
-      <c r="M148" s="394" t="n"/>
-      <c r="N148" s="394" t="n"/>
-      <c r="O148" s="394" t="n"/>
-      <c r="P148" s="394" t="n"/>
-      <c r="Q148" s="394" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="420" t="inlineStr">
-        <is>
-          <t>Statement For Selected Period</t>
-        </is>
-      </c>
-      <c r="B149" s="394" t="n"/>
-      <c r="C149" s="420" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="D149" s="420" t="n"/>
-      <c r="E149" s="420" t="n"/>
-      <c r="F149" s="394" t="n"/>
-      <c r="G149" s="394" t="n"/>
+      <c r="B149" s="358" t="n"/>
+      <c r="C149" s="355" t="n"/>
+      <c r="D149" s="394" t="n"/>
+      <c r="E149" s="394" t="n"/>
+      <c r="F149" s="118" t="n"/>
+      <c r="G149" s="118" t="n"/>
       <c r="H149" s="394" t="n"/>
-      <c r="I149" s="394" t="n"/>
+      <c r="I149" s="11" t="n"/>
       <c r="J149" s="394" t="n"/>
       <c r="K149" s="394" t="n"/>
       <c r="L149" s="394" t="n"/>
@@ -36755,39 +37025,41 @@
       <c r="Q149" s="394" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
-        </is>
-      </c>
-      <c r="B150" s="56" t="n"/>
-      <c r="C150" s="56" t="n">
-        <v>52613.88</v>
-      </c>
-      <c r="D150" s="56" t="n"/>
-      <c r="E150" s="56" t="n"/>
-      <c r="F150" s="56" t="n"/>
-      <c r="G150" s="56" t="n"/>
-      <c r="H150" s="56" t="n"/>
-      <c r="I150" s="56" t="n"/>
-      <c r="J150" s="56" t="n"/>
-      <c r="K150" s="56" t="n"/>
-      <c r="L150" s="56" t="n"/>
-      <c r="M150" s="56" t="n"/>
-      <c r="N150" s="56" t="n"/>
-      <c r="O150" s="56" t="n"/>
-      <c r="P150" s="56" t="n"/>
-      <c r="Q150" s="56" t="n"/>
+      <c r="A150" s="420" t="inlineStr">
+        <is>
+          <t>Statement For Selected Period</t>
+        </is>
+      </c>
+      <c r="B150" s="394" t="n"/>
+      <c r="C150" s="420" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="D150" s="420" t="n"/>
+      <c r="E150" s="420" t="n"/>
+      <c r="F150" s="394" t="n"/>
+      <c r="G150" s="394" t="n"/>
+      <c r="H150" s="394" t="n"/>
+      <c r="I150" s="394" t="n"/>
+      <c r="J150" s="394" t="n"/>
+      <c r="K150" s="394" t="n"/>
+      <c r="L150" s="394" t="n"/>
+      <c r="M150" s="394" t="n"/>
+      <c r="N150" s="394" t="n"/>
+      <c r="O150" s="394" t="n"/>
+      <c r="P150" s="394" t="n"/>
+      <c r="Q150" s="394" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B151" s="56" t="n"/>
-      <c r="C151" s="394" t="n">
-        <v>88000.02</v>
+      <c r="C151" s="56" t="n">
+        <v>52613.88</v>
       </c>
       <c r="D151" s="56" t="n"/>
       <c r="E151" s="56" t="n"/>
@@ -36807,12 +37079,12 @@
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B152" s="56" t="n"/>
       <c r="C152" s="394" t="n">
-        <v>57392.81999999999</v>
+        <v>88000.02</v>
       </c>
       <c r="D152" s="56" t="n"/>
       <c r="E152" s="56" t="n"/>
@@ -36832,12 +37104,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>Mar 30 - Apr 05 2026</t>
+          <t>Mar 23 - Mar 29 2026</t>
         </is>
       </c>
       <c r="B153" s="56" t="n"/>
       <c r="C153" s="394" t="n">
-        <v>75773.69</v>
+        <v>57392.81999999999</v>
       </c>
       <c r="D153" s="56" t="n"/>
       <c r="E153" s="56" t="n"/>
@@ -36855,14 +37127,14 @@
       <c r="Q153" s="56" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Apr 06 - Apr 12</t>
-        </is>
-      </c>
-      <c r="B154" s="394" t="n"/>
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>Mar 30 - Apr 05 2026</t>
+        </is>
+      </c>
+      <c r="B154" s="56" t="n"/>
       <c r="C154" s="394" t="n">
-        <v>56910.23</v>
+        <v>75773.69</v>
       </c>
       <c r="D154" s="56" t="n"/>
       <c r="E154" s="56" t="n"/>
@@ -36880,68 +37152,93 @@
       <c r="Q154" s="56" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="325" t="inlineStr">
-        <is>
-          <t>Apr 13 - Apr 19</t>
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Apr 06 - Apr 12</t>
         </is>
       </c>
       <c r="B155" s="394" t="n"/>
       <c r="C155" s="394" t="n">
-        <v>58051.89</v>
-      </c>
+        <v>56910.23</v>
+      </c>
+      <c r="D155" s="56" t="n"/>
+      <c r="E155" s="56" t="n"/>
+      <c r="F155" s="56" t="n"/>
+      <c r="G155" s="56" t="n"/>
+      <c r="H155" s="56" t="n"/>
+      <c r="I155" s="56" t="n"/>
+      <c r="J155" s="56" t="n"/>
+      <c r="K155" s="56" t="n"/>
+      <c r="L155" s="56" t="n"/>
+      <c r="M155" s="56" t="n"/>
+      <c r="N155" s="56" t="n"/>
+      <c r="O155" s="56" t="n"/>
+      <c r="P155" s="56" t="n"/>
+      <c r="Q155" s="56" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="11" t="inlineStr">
-        <is>
-          <t>Apr 20 - Apr 26</t>
+      <c r="A156" s="325" t="inlineStr">
+        <is>
+          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B156" s="394" t="n"/>
       <c r="C156" s="394" t="n">
-        <v>56750.23</v>
+        <v>58051.89</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="394" t="inlineStr">
-        <is>
-          <t>Apr 27 - May 03</t>
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>Apr 20 - Apr 26</t>
         </is>
       </c>
       <c r="B157" s="394" t="n"/>
       <c r="C157" s="394" t="n">
+        <v>56750.23</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="394" t="inlineStr">
+        <is>
+          <t>Apr 27 - May 03</t>
+        </is>
+      </c>
+      <c r="B158" s="394" t="n"/>
+      <c r="C158" s="394" t="n">
         <v>57253.16</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="471" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="471" t="inlineStr">
         <is>
           <t>May 4 - May 10</t>
         </is>
       </c>
-      <c r="B158" s="471" t="n"/>
-      <c r="C158" s="471" t="n">
+      <c r="B159" s="471" t="n"/>
+      <c r="C159" s="471" t="n">
         <v>60756.22</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="474" t="inlineStr">
-        <is>
-          <t>May 11 - May 17</t>
-        </is>
-      </c>
-      <c r="B159" s="474" t="n"/>
-      <c r="C159" s="474" t="n">
-        <v>54781.81</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="474" t="inlineStr">
         <is>
-          <t>May 18 - May 24</t>
+          <t>May 11 - May 17</t>
         </is>
       </c>
       <c r="B160" s="474" t="n"/>
       <c r="C160" s="474" t="n">
+        <v>54781.81</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="474" t="inlineStr">
+        <is>
+          <t>May 18 - May 24</t>
+        </is>
+      </c>
+      <c r="B161" s="474" t="n"/>
+      <c r="C161" s="474" t="n">
         <v>63431.41</v>
       </c>
     </row>
@@ -36959,7 +37256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S164"/>
+  <dimension ref="A1:S165"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col width="33.6640625" customWidth="1" style="69" min="1" max="1"/>
@@ -42245,121 +42542,127 @@
       <c r="S147" s="69" t="n"/>
     </row>
     <row r="148" ht="27.6" customHeight="1">
-      <c r="A148" s="474" t="n"/>
+      <c r="A148" s="474" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B148" s="545" t="n"/>
       <c r="C148" s="398" t="n"/>
       <c r="D148" s="398" t="n"/>
-      <c r="E148" s="2" t="n"/>
-      <c r="F148" s="2" t="n"/>
-      <c r="G148" s="544" t="n"/>
-      <c r="H148" s="544" t="n"/>
-      <c r="I148" s="544" t="n"/>
-      <c r="J148" s="118" t="n"/>
+      <c r="E148" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>9696.33</v>
+      </c>
+      <c r="G148" s="544" t="n">
+        <v>6451.75</v>
+      </c>
+      <c r="H148" s="544" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="544" t="n">
+        <v>52.77</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3191.81</v>
+      </c>
       <c r="K148" s="406" t="n"/>
       <c r="L148" s="94" t="n"/>
       <c r="M148" s="472" t="n"/>
       <c r="N148" s="472" t="n"/>
-      <c r="O148" s="114" t="n"/>
+      <c r="S148" s="69" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="315" t="inlineStr">
+      <c r="A149" s="474" t="n"/>
+      <c r="B149" s="545" t="n"/>
+      <c r="C149" s="398" t="n"/>
+      <c r="D149" s="398" t="n"/>
+      <c r="E149" s="2" t="n"/>
+      <c r="F149" s="2" t="n"/>
+      <c r="G149" s="544" t="n"/>
+      <c r="H149" s="544" t="n"/>
+      <c r="I149" s="544" t="n"/>
+      <c r="J149" s="118" t="n"/>
+      <c r="K149" s="406" t="n"/>
+      <c r="L149" s="94" t="n"/>
+      <c r="M149" s="472" t="n"/>
+      <c r="N149" s="472" t="n"/>
+      <c r="O149" s="114" t="n"/>
+      <c r="S149" s="69" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="315" t="inlineStr">
         <is>
           <t>Markham</t>
         </is>
       </c>
-      <c r="B149" s="358" t="n"/>
-      <c r="C149" s="358" t="n"/>
-      <c r="D149" s="355" t="n"/>
-      <c r="E149" s="315" t="n"/>
-      <c r="F149" s="315" t="n"/>
-      <c r="G149" s="118" t="n"/>
-      <c r="H149" s="118" t="n"/>
-      <c r="I149" s="11" t="n"/>
-      <c r="J149" s="118" t="n"/>
-      <c r="K149" s="118" t="n"/>
-      <c r="L149" s="118" t="n"/>
-      <c r="M149" s="118" t="n"/>
-      <c r="N149" s="118" t="n"/>
-      <c r="O149" s="114" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="316" t="inlineStr">
+      <c r="B150" s="358" t="n"/>
+      <c r="C150" s="358" t="n"/>
+      <c r="D150" s="355" t="n"/>
+      <c r="E150" s="315" t="n"/>
+      <c r="F150" s="315" t="n"/>
+      <c r="G150" s="118" t="n"/>
+      <c r="H150" s="118" t="n"/>
+      <c r="I150" s="11" t="n"/>
+      <c r="J150" s="118" t="n"/>
+      <c r="K150" s="118" t="n"/>
+      <c r="L150" s="118" t="n"/>
+      <c r="M150" s="118" t="n"/>
+      <c r="N150" s="118" t="n"/>
+      <c r="O150" s="114" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="316" t="inlineStr">
         <is>
           <t>Statement For Selected Period</t>
         </is>
       </c>
-      <c r="B150" s="316" t="inlineStr">
+      <c r="B151" s="316" t="inlineStr">
         <is>
           <t>Total Revenue (Net Sales)</t>
         </is>
       </c>
-      <c r="C150" s="316" t="inlineStr">
+      <c r="C151" s="316" t="inlineStr">
         <is>
           <t>Royalties
 (6%) +HST</t>
         </is>
       </c>
-      <c r="D150" s="316" t="inlineStr">
+      <c r="D151" s="316" t="inlineStr">
         <is>
           <t>Marketing
 (2%) +HST</t>
         </is>
       </c>
-      <c r="E150" s="316" t="n"/>
-      <c r="F150" s="316" t="n"/>
-      <c r="G150" s="170" t="n"/>
-      <c r="H150" s="170" t="n"/>
-      <c r="I150" s="170" t="n"/>
-      <c r="J150" s="170" t="n"/>
-      <c r="K150" s="364" t="n"/>
-      <c r="L150" s="364" t="n"/>
-      <c r="M150" s="364" t="n"/>
-      <c r="N150" s="364" t="n"/>
-      <c r="O150" s="193" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
-        </is>
-      </c>
-      <c r="B151" s="389" t="n">
-        <v>8820.769999999999</v>
-      </c>
-      <c r="C151" s="398">
-        <f>(B146*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D151" s="398">
-        <f>(B146*0.02)*1.13</f>
-        <v/>
-      </c>
-      <c r="E151" s="118" t="n"/>
-      <c r="F151" s="118" t="n"/>
-      <c r="G151" s="118" t="n"/>
-      <c r="H151" s="118" t="n"/>
-      <c r="I151" s="118" t="n"/>
-      <c r="J151" s="118" t="n"/>
-      <c r="K151" s="118" t="n"/>
-      <c r="L151" s="118" t="n"/>
-      <c r="M151" s="118" t="n"/>
-      <c r="N151" s="118" t="n"/>
+      <c r="E151" s="316" t="n"/>
+      <c r="F151" s="316" t="n"/>
+      <c r="G151" s="170" t="n"/>
+      <c r="H151" s="170" t="n"/>
+      <c r="I151" s="170" t="n"/>
+      <c r="J151" s="170" t="n"/>
+      <c r="K151" s="364" t="n"/>
+      <c r="L151" s="364" t="n"/>
+      <c r="M151" s="364" t="n"/>
+      <c r="N151" s="364" t="n"/>
+      <c r="O151" s="193" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B152" s="389" t="n">
-        <v>10355.46</v>
+        <v>8820.769999999999</v>
       </c>
       <c r="C152" s="398">
-        <f>(B147*0.06)*1.13</f>
+        <f>(B146*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D152" s="398">
-        <f>(B147*0.02)*1.13</f>
+        <f>(B146*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E152" s="118" t="n"/>
@@ -42376,18 +42679,18 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B153" s="389" t="n">
-        <v>9315.370000000001</v>
+        <v>10355.46</v>
       </c>
       <c r="C153" s="398">
-        <f>(B148*0.06)*1.13</f>
+        <f>(B147*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D153" s="398">
-        <f>(B148*0.02)*1.13</f>
+        <f>(B147*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E153" s="118" t="n"/>
@@ -42404,18 +42707,18 @@
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>Mar 30 - Apr 05 2026</t>
+          <t>Mar 23 - Mar 29 2026</t>
         </is>
       </c>
       <c r="B154" s="389" t="n">
-        <v>10351.65</v>
+        <v>9315.370000000001</v>
       </c>
       <c r="C154" s="398">
-        <f>(B149*0.06)*1.13</f>
+        <f>(B148*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D154" s="398">
-        <f>(B149*0.02)*1.13</f>
+        <f>(B148*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E154" s="118" t="n"/>
@@ -42430,134 +42733,156 @@
       <c r="N154" s="118" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>Mar 30 - Apr 05 2026</t>
+        </is>
+      </c>
+      <c r="B155" s="389" t="n">
+        <v>10351.65</v>
+      </c>
+      <c r="C155" s="398">
+        <f>(B149*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D155" s="398">
+        <f>(B149*0.02)*1.13</f>
+        <v/>
+      </c>
+      <c r="E155" s="118" t="n"/>
+      <c r="F155" s="118" t="n"/>
+      <c r="G155" s="118" t="n"/>
+      <c r="H155" s="118" t="n"/>
+      <c r="I155" s="118" t="n"/>
+      <c r="J155" s="118" t="n"/>
+      <c r="K155" s="118" t="n"/>
+      <c r="L155" s="118" t="n"/>
+      <c r="M155" s="118" t="n"/>
+      <c r="N155" s="118" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Apr 06 - Apr 12</t>
         </is>
       </c>
-      <c r="B155" s="389" t="n">
+      <c r="B156" s="389" t="n">
         <v>9459.860000000001</v>
       </c>
-      <c r="C155" s="398">
+      <c r="C156" s="398">
         <f>(B150*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D155" s="398">
+      <c r="D156" s="398">
         <f>(B150*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="325" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="325" t="inlineStr">
         <is>
           <t>Apr 13 - Apr 19</t>
         </is>
       </c>
-      <c r="B156" s="389" t="n">
+      <c r="B157" s="389" t="n">
         <v>10085.15</v>
       </c>
-      <c r="C156" s="398">
+      <c r="C157" s="398">
         <f>(B151*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D156" s="398">
+      <c r="D157" s="398">
         <f>(B151*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="11" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="11" t="inlineStr">
         <is>
           <t>Apr 20 - Apr 26</t>
         </is>
       </c>
-      <c r="B157" s="389" t="n">
+      <c r="B158" s="389" t="n">
         <v>9520.02</v>
       </c>
-      <c r="C157" s="398">
+      <c r="C158" s="398">
         <f>(B152*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D157" s="398">
+      <c r="D158" s="398">
         <f>(B152*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="394" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="394" t="inlineStr">
         <is>
           <t>Apr 27 - May 03</t>
         </is>
       </c>
-      <c r="B158" s="389" t="n">
+      <c r="B159" s="389" t="n">
         <v>9642.91</v>
       </c>
-      <c r="C158" s="398">
+      <c r="C159" s="398">
         <f>(B154*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D158" s="398">
+      <c r="D159" s="398">
         <f>(B154*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="471" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="471" t="inlineStr">
         <is>
           <t>May 4 - May 10</t>
         </is>
       </c>
-      <c r="B159" s="472" t="n">
+      <c r="B160" s="472" t="n">
         <v>9248.879999999999</v>
       </c>
-      <c r="C159" s="398">
+      <c r="C160" s="398">
         <f>(B155*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D159" s="398">
+      <c r="D160" s="398">
         <f>(B155*0.02)*1.13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="474" t="inlineStr">
-        <is>
-          <t>May 11 - May 17</t>
-        </is>
-      </c>
-      <c r="B160" s="545" t="n">
-        <v>8663.619999999999</v>
-      </c>
-      <c r="C160" s="398">
-        <f>(B157*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D160" s="398">
-        <f>(B157*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="474" t="inlineStr">
         <is>
+          <t>May 11 - May 17</t>
+        </is>
+      </c>
+      <c r="B161" s="545" t="n">
+        <v>8663.619999999999</v>
+      </c>
+      <c r="C161" s="398">
+        <f>(B157*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D161" s="398">
+        <f>(B157*0.02)*1.13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="474" t="inlineStr">
+        <is>
           <t>May 18 - May 24</t>
         </is>
       </c>
-      <c r="B161" s="545" t="n">
+      <c r="B162" s="545" t="n">
         <v>8852.700000000001</v>
       </c>
-      <c r="C161" s="398" t="n">
+      <c r="C162" s="398" t="n">
         <v>600.2130599999999</v>
       </c>
-      <c r="D161" s="398" t="n">
+      <c r="D162" s="398" t="n">
         <v>200.07102</v>
       </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="474" t="n"/>
-      <c r="B162" s="545" t="n"/>
-      <c r="C162" s="398" t="n"/>
-      <c r="D162" s="398" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="474" t="n"/>
@@ -42570,6 +42895,12 @@
       <c r="B164" s="545" t="n"/>
       <c r="C164" s="398" t="n"/>
       <c r="D164" s="398" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="474" t="n"/>
+      <c r="B165" s="545" t="n"/>
+      <c r="C165" s="398" t="n"/>
+      <c r="D165" s="398" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -42585,7 +42916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB127"/>
+  <dimension ref="A1:AB128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.109375" customWidth="1" style="382" min="1" max="1"/>
@@ -47548,16 +47879,32 @@
       <c r="AB113" s="402" t="n"/>
     </row>
     <row r="114" ht="41.4" customHeight="1">
-      <c r="A114" s="474" t="n"/>
+      <c r="A114" s="474" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B114" s="478" t="n"/>
       <c r="C114" s="471" t="n"/>
       <c r="D114" s="471" t="n"/>
-      <c r="E114" s="402" t="n"/>
-      <c r="F114" s="402" t="n"/>
-      <c r="G114" s="402" t="n"/>
-      <c r="H114" s="402" t="n"/>
-      <c r="I114" s="402" t="n"/>
-      <c r="J114" s="402" t="n"/>
+      <c r="E114" s="402" t="n">
+        <v>681</v>
+      </c>
+      <c r="F114" s="402" t="n">
+        <v>18212.5</v>
+      </c>
+      <c r="G114" s="402" t="n">
+        <v>13790.83</v>
+      </c>
+      <c r="H114" s="402" t="n">
+        <v>229.05</v>
+      </c>
+      <c r="I114" s="402" t="n">
+        <v>221.08</v>
+      </c>
+      <c r="J114" s="402" t="n">
+        <v>3971.54</v>
+      </c>
       <c r="K114" s="406" t="n"/>
       <c r="L114" s="406" t="n"/>
       <c r="M114" s="338" t="n"/>
@@ -47578,244 +47925,274 @@
       <c r="AB114" s="402" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="546" t="inlineStr">
+      <c r="A115" s="474" t="n"/>
+      <c r="B115" s="478" t="n"/>
+      <c r="C115" s="471" t="n"/>
+      <c r="D115" s="471" t="n"/>
+      <c r="E115" s="402" t="n"/>
+      <c r="F115" s="402" t="n"/>
+      <c r="G115" s="402" t="n"/>
+      <c r="H115" s="402" t="n"/>
+      <c r="I115" s="402" t="n"/>
+      <c r="J115" s="402" t="n"/>
+      <c r="K115" s="406" t="n"/>
+      <c r="L115" s="406" t="n"/>
+      <c r="M115" s="338" t="n"/>
+      <c r="N115" s="402" t="n"/>
+      <c r="O115" s="472" t="n"/>
+      <c r="P115" s="472" t="n"/>
+      <c r="Q115" s="402" t="n"/>
+      <c r="R115" s="402" t="n"/>
+      <c r="S115" s="402" t="n"/>
+      <c r="T115" s="402" t="n"/>
+      <c r="U115" s="402" t="n"/>
+      <c r="V115" s="402" t="n"/>
+      <c r="W115" s="402" t="n"/>
+      <c r="X115" s="402" t="n"/>
+      <c r="Y115" s="402" t="n"/>
+      <c r="Z115" s="402" t="n"/>
+      <c r="AA115" s="402" t="n"/>
+      <c r="AB115" s="402" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="546" t="inlineStr">
         <is>
           <t>Wonderland</t>
         </is>
       </c>
-      <c r="B115" s="358" t="n"/>
-      <c r="C115" s="358" t="n"/>
-      <c r="D115" s="355" t="n"/>
-      <c r="E115" s="546" t="n"/>
-      <c r="F115" s="546" t="n"/>
-      <c r="G115" s="118" t="n"/>
-      <c r="H115" s="118" t="n"/>
-      <c r="I115" s="11" t="n"/>
-      <c r="J115" s="118" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="415" t="inlineStr">
+      <c r="B116" s="358" t="n"/>
+      <c r="C116" s="358" t="n"/>
+      <c r="D116" s="355" t="n"/>
+      <c r="E116" s="546" t="n"/>
+      <c r="F116" s="546" t="n"/>
+      <c r="G116" s="118" t="n"/>
+      <c r="H116" s="118" t="n"/>
+      <c r="I116" s="11" t="n"/>
+      <c r="J116" s="118" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="415" t="inlineStr">
         <is>
           <t>Statement For Selected Period</t>
         </is>
       </c>
-      <c r="B116" s="415" t="inlineStr">
+      <c r="B117" s="415" t="inlineStr">
         <is>
           <t>Total Revenue (Net Sales)</t>
         </is>
       </c>
-      <c r="C116" s="415" t="inlineStr">
+      <c r="C117" s="415" t="inlineStr">
         <is>
           <t>Royalties
 (6%) +HST</t>
         </is>
       </c>
-      <c r="D116" s="415" t="inlineStr">
+      <c r="D117" s="415" t="inlineStr">
         <is>
           <t>Marketing
 (2%) +HST</t>
         </is>
       </c>
-      <c r="E116" s="415" t="n"/>
-      <c r="F116" s="415" t="n"/>
-      <c r="K116" s="118" t="n"/>
-      <c r="L116" s="389" t="n"/>
-      <c r="M116" s="389" t="n"/>
-      <c r="N116" s="389" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
-        </is>
-      </c>
-      <c r="B117" s="382" t="n">
-        <v>9468.790000000001</v>
-      </c>
-      <c r="C117" s="394">
-        <f>(B112*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D117" s="394">
-        <f>(B112*0.02)*1.13</f>
-        <v/>
-      </c>
+      <c r="E117" s="415" t="n"/>
+      <c r="F117" s="415" t="n"/>
+      <c r="K117" s="118" t="n"/>
+      <c r="L117" s="389" t="n"/>
+      <c r="M117" s="389" t="n"/>
+      <c r="N117" s="389" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B118" s="382" t="n">
-        <v>11279.79</v>
+        <v>9468.790000000001</v>
       </c>
       <c r="C118" s="394">
-        <f>(B113*0.06)*1.13</f>
+        <f>(B112*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D118" s="394">
-        <f>(B113*0.02)*1.13</f>
+        <f>(B112*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B119" s="382" t="n">
-        <v>10723.8</v>
+        <v>11279.79</v>
       </c>
       <c r="C119" s="394">
-        <f>(B114*0.06)*1.13</f>
+        <f>(B113*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D119" s="394">
-        <f>(B114*0.02)*1.13</f>
+        <f>(B113*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
+          <t>Mar 23 - Mar 29 2026</t>
+        </is>
+      </c>
+      <c r="B120" s="382" t="n">
+        <v>10723.8</v>
+      </c>
+      <c r="C120" s="394">
+        <f>(B114*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D120" s="394">
+        <f>(B114*0.02)*1.13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
           <t>Mar 30 - Apr 05 2026</t>
         </is>
       </c>
-      <c r="B120" s="382" t="n">
+      <c r="B121" s="382" t="n">
         <v>12777.21</v>
       </c>
-      <c r="C120" s="394">
+      <c r="C121" s="394">
         <f>(B115*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D120" s="394">
+      <c r="D121" s="394">
         <f>(B115*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Apr 06 - Apr 12</t>
         </is>
       </c>
-      <c r="B121" s="382" t="n">
+      <c r="B122" s="382" t="n">
         <v>10184.66</v>
       </c>
-      <c r="C121" s="394">
+      <c r="C122" s="394">
         <f>(B116*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D121" s="394">
+      <c r="D122" s="394">
         <f>(B116*0.02)*1.13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t>Apr 13 - Apr 19</t>
-        </is>
-      </c>
-      <c r="B122" s="382" t="n">
-        <v>11746.55</v>
-      </c>
-      <c r="C122" s="394">
-        <f>(B117*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D122" s="394">
-        <f>(B117*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
+          <t>Apr 13 - Apr 19</t>
+        </is>
+      </c>
+      <c r="B123" s="382" t="n">
+        <v>11746.55</v>
+      </c>
+      <c r="C123" s="394">
+        <f>(B117*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D123" s="394">
+        <f>(B117*0.02)*1.13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
           <t>Apr 20 - Apr 26</t>
         </is>
       </c>
-      <c r="B123" s="382" t="n">
+      <c r="B124" s="382" t="n">
         <v>12617.9</v>
       </c>
-      <c r="C123" s="394">
+      <c r="C124" s="394">
         <f>(B118*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D123" s="394">
+      <c r="D124" s="394">
         <f>(B118*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="394" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="394" t="inlineStr">
         <is>
           <t>Apr 27 - May 03</t>
         </is>
       </c>
-      <c r="B124" s="382" t="n">
+      <c r="B125" s="382" t="n">
         <v>12032.49</v>
       </c>
-      <c r="C124" s="394">
+      <c r="C125" s="394">
         <f>(B120*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D124" s="394">
+      <c r="D125" s="394">
         <f>(B120*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="471" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="471" t="inlineStr">
         <is>
           <t>May 4 - May 10</t>
         </is>
       </c>
-      <c r="B125" s="382" t="n">
+      <c r="B126" s="382" t="n">
         <v>14392.2</v>
       </c>
-      <c r="C125" s="394">
+      <c r="C126" s="394">
         <f>(B121*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D125" s="394">
+      <c r="D126" s="394">
         <f>(B121*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="474" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="474" t="inlineStr">
         <is>
           <t>May 11 - May 17</t>
         </is>
       </c>
-      <c r="B126" s="478" t="n">
+      <c r="B127" s="478" t="n">
         <v>17935.11</v>
       </c>
-      <c r="C126" s="394">
+      <c r="C127" s="394">
         <f>(B123*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D126" s="394">
+      <c r="D127" s="394">
         <f>(B123*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="382" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="382" t="inlineStr">
         <is>
           <t>May 18 - May 24</t>
         </is>
       </c>
-      <c r="B127" s="382" t="n">
+      <c r="B128" s="382" t="n">
         <v>17172.29</v>
       </c>
-      <c r="C127" s="382" t="n">
+      <c r="C128" s="382" t="n">
         <v>1164.281262</v>
       </c>
-      <c r="D127" s="382" t="n">
+      <c r="D128" s="382" t="n">
         <v>388.0937539999999</v>
       </c>
     </row>
@@ -47833,7 +48210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC108"/>
+  <dimension ref="A1:AC109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="40.5546875" customWidth="1" style="408" min="1" max="1"/>
@@ -52225,16 +52602,32 @@
       <c r="AC91" s="550" t="n"/>
     </row>
     <row r="92" ht="27.6" customHeight="1">
-      <c r="A92" s="353" t="n"/>
+      <c r="A92" s="353" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B92" s="474" t="n"/>
       <c r="C92" s="399" t="n"/>
       <c r="D92" s="399" t="n"/>
-      <c r="E92" s="322" t="n"/>
-      <c r="F92" s="550" t="n"/>
-      <c r="G92" s="550" t="n"/>
-      <c r="H92" s="550" t="n"/>
-      <c r="I92" s="550" t="n"/>
-      <c r="J92" s="550" t="n"/>
+      <c r="E92" s="322" t="n">
+        <v>275</v>
+      </c>
+      <c r="F92" s="550" t="n">
+        <v>9049.299999999999</v>
+      </c>
+      <c r="G92" s="550" t="n">
+        <v>6214.83</v>
+      </c>
+      <c r="H92" s="550" t="n">
+        <v>158.35</v>
+      </c>
+      <c r="I92" s="550" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="J92" s="550" t="n">
+        <v>2312.83</v>
+      </c>
       <c r="K92" s="405" t="n"/>
       <c r="L92" s="550" t="n"/>
       <c r="M92" s="550" t="n"/>
@@ -52256,52 +52649,47 @@
       <c r="AC92" s="550" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="399" t="inlineStr">
+      <c r="A93" s="353" t="n"/>
+      <c r="B93" s="474" t="n"/>
+      <c r="C93" s="399" t="n"/>
+      <c r="D93" s="399" t="n"/>
+      <c r="E93" s="322" t="n"/>
+      <c r="F93" s="550" t="n"/>
+      <c r="G93" s="550" t="n"/>
+      <c r="H93" s="550" t="n"/>
+      <c r="I93" s="550" t="n"/>
+      <c r="J93" s="550" t="n"/>
+      <c r="K93" s="405" t="n"/>
+      <c r="L93" s="550" t="n"/>
+      <c r="M93" s="550" t="n"/>
+      <c r="N93" s="550" t="n"/>
+      <c r="O93" s="472" t="n"/>
+      <c r="P93" s="472" t="n"/>
+      <c r="Q93" s="550" t="n"/>
+      <c r="R93" s="550" t="n"/>
+      <c r="S93" s="550" t="n"/>
+      <c r="T93" s="550" t="n"/>
+      <c r="U93" s="550" t="n"/>
+      <c r="V93" s="550" t="n"/>
+      <c r="W93" s="550" t="n"/>
+      <c r="X93" s="550" t="n"/>
+      <c r="Y93" s="550" t="n"/>
+      <c r="Z93" s="550" t="n"/>
+      <c r="AA93" s="550" t="n"/>
+      <c r="AB93" s="550" t="n"/>
+      <c r="AC93" s="550" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="399" t="inlineStr">
         <is>
           <t>Ajax</t>
         </is>
       </c>
-      <c r="B93" s="358" t="n"/>
-      <c r="C93" s="358" t="n"/>
-      <c r="D93" s="355" t="n"/>
-      <c r="E93" s="45" t="n"/>
-      <c r="F93" s="45" t="n"/>
-      <c r="G93" s="389" t="n"/>
-      <c r="H93" s="56" t="n"/>
-      <c r="I93" s="56" t="n"/>
-      <c r="J93" s="56" t="n"/>
-      <c r="K93" s="56" t="n"/>
-      <c r="L93" s="56" t="n"/>
-      <c r="M93" s="56" t="n"/>
-      <c r="N93" s="56" t="n"/>
-      <c r="O93" s="56" t="n"/>
-      <c r="P93" s="56" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="479" t="inlineStr">
-        <is>
-          <t>Statement For Selected Period</t>
-        </is>
-      </c>
-      <c r="B94" s="479" t="inlineStr">
-        <is>
-          <t>Total Revenue (Net Sales)</t>
-        </is>
-      </c>
-      <c r="C94" s="479" t="inlineStr">
-        <is>
-          <t>Royalties
-(6%) +HST</t>
-        </is>
-      </c>
-      <c r="D94" s="479" t="inlineStr">
-        <is>
-          <t>Marketing
-(2%) +HST</t>
-        </is>
-      </c>
-      <c r="E94" s="30" t="n"/>
-      <c r="F94" s="30" t="n"/>
+      <c r="B94" s="358" t="n"/>
+      <c r="C94" s="358" t="n"/>
+      <c r="D94" s="355" t="n"/>
+      <c r="E94" s="45" t="n"/>
+      <c r="F94" s="45" t="n"/>
       <c r="G94" s="389" t="n"/>
       <c r="H94" s="56" t="n"/>
       <c r="I94" s="56" t="n"/>
@@ -52314,25 +52702,31 @@
       <c r="P94" s="56" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
-        </is>
-      </c>
-      <c r="B95" s="394" t="n">
-        <v>9629.730000000001</v>
-      </c>
-      <c r="C95" s="399">
-        <f>(B90*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D95" s="399">
-        <f>(B90*0.02)*1.13</f>
-        <v/>
-      </c>
-      <c r="E95" s="56" t="n"/>
-      <c r="F95" s="56" t="n"/>
-      <c r="G95" s="56" t="n"/>
+      <c r="A95" s="479" t="inlineStr">
+        <is>
+          <t>Statement For Selected Period</t>
+        </is>
+      </c>
+      <c r="B95" s="479" t="inlineStr">
+        <is>
+          <t>Total Revenue (Net Sales)</t>
+        </is>
+      </c>
+      <c r="C95" s="479" t="inlineStr">
+        <is>
+          <t>Royalties
+(6%) +HST</t>
+        </is>
+      </c>
+      <c r="D95" s="479" t="inlineStr">
+        <is>
+          <t>Marketing
+(2%) +HST</t>
+        </is>
+      </c>
+      <c r="E95" s="30" t="n"/>
+      <c r="F95" s="30" t="n"/>
+      <c r="G95" s="389" t="n"/>
       <c r="H95" s="56" t="n"/>
       <c r="I95" s="56" t="n"/>
       <c r="J95" s="56" t="n"/>
@@ -52346,18 +52740,18 @@
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B96" s="394" t="n">
-        <v>11058.63</v>
+        <v>9629.730000000001</v>
       </c>
       <c r="C96" s="399">
-        <f>(B91*0.06)*1.13</f>
+        <f>(B90*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D96" s="399">
-        <f>(B91*0.02)*1.13</f>
+        <f>(B90*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E96" s="56" t="n"/>
@@ -52376,18 +52770,18 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B97" s="394" t="n">
-        <v>8345.030000000001</v>
+        <v>11058.63</v>
       </c>
       <c r="C97" s="399">
-        <f>(B92*0.06)*1.13</f>
+        <f>(B91*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D97" s="399">
-        <f>(B92*0.02)*1.13</f>
+        <f>(B91*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E97" s="56" t="n"/>
@@ -52406,18 +52800,18 @@
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>Mar 30 - Apr 05 2026</t>
+          <t>Mar 23 - Mar 29 2026</t>
         </is>
       </c>
       <c r="B98" s="394" t="n">
-        <v>9875.25</v>
+        <v>8345.030000000001</v>
       </c>
       <c r="C98" s="399">
-        <f>(B93*0.06)*1.13</f>
+        <f>(B92*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D98" s="399">
-        <f>(B93*0.02)*1.13</f>
+        <f>(B92*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E98" s="56" t="n"/>
@@ -52434,146 +52828,176 @@
       <c r="P98" s="56" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>Mar 30 - Apr 05 2026</t>
+        </is>
+      </c>
+      <c r="B99" s="394" t="n">
+        <v>9875.25</v>
+      </c>
+      <c r="C99" s="399">
+        <f>(B93*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D99" s="399">
+        <f>(B93*0.02)*1.13</f>
+        <v/>
+      </c>
+      <c r="E99" s="56" t="n"/>
+      <c r="F99" s="56" t="n"/>
+      <c r="G99" s="56" t="n"/>
+      <c r="H99" s="56" t="n"/>
+      <c r="I99" s="56" t="n"/>
+      <c r="J99" s="56" t="n"/>
+      <c r="K99" s="56" t="n"/>
+      <c r="L99" s="56" t="n"/>
+      <c r="M99" s="56" t="n"/>
+      <c r="N99" s="56" t="n"/>
+      <c r="O99" s="56" t="n"/>
+      <c r="P99" s="56" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Apr 06 - Apr 12</t>
         </is>
       </c>
-      <c r="B99" s="394" t="n">
+      <c r="B100" s="394" t="n">
         <v>8969.310000000001</v>
       </c>
-      <c r="C99" s="399">
+      <c r="C100" s="399">
         <f>(B94*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D99" s="399">
+      <c r="D100" s="399">
         <f>(B94*0.02)*1.13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t>Apr 13 - Apr 19</t>
-        </is>
-      </c>
-      <c r="B100" s="394" t="n">
-        <v>8563.719999999999</v>
-      </c>
-      <c r="C100" s="399">
-        <f>(B95*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D100" s="399">
-        <f>(B95*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>Apr 20 - Apr 26</t>
+          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B101" s="394" t="n">
-        <v>7472.82</v>
+        <v>8563.719999999999</v>
       </c>
       <c r="C101" s="399">
-        <f>(B96*0.06)*1.13</f>
+        <f>(B95*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D101" s="399">
-        <f>(B96*0.02)*1.13</f>
+        <f>(B95*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
+          <t>Apr 20 - Apr 26</t>
+        </is>
+      </c>
+      <c r="B102" s="394" t="n">
+        <v>7472.82</v>
+      </c>
+      <c r="C102" s="399">
+        <f>(B96*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D102" s="399">
+        <f>(B96*0.02)*1.13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
           <t>Apr 27 - May 03</t>
         </is>
       </c>
-      <c r="B102" s="394" t="n">
+      <c r="B103" s="394" t="n">
         <v>8601.07</v>
       </c>
-      <c r="C102" s="399">
+      <c r="C103" s="399">
         <f>(B98*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D102" s="399">
+      <c r="D103" s="399">
         <f>(B98*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="334" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="334" t="inlineStr">
         <is>
           <t>May 4 - May 10</t>
         </is>
       </c>
-      <c r="B103" s="471" t="n">
+      <c r="B104" s="471" t="n">
         <v>9769.83</v>
       </c>
-      <c r="C103" s="399">
+      <c r="C104" s="399">
         <f>(B99*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D103" s="399">
+      <c r="D104" s="399">
         <f>(B99*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="353" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="353" t="inlineStr">
         <is>
           <t>May 11 - May 17</t>
         </is>
       </c>
-      <c r="B104" s="474" t="n">
+      <c r="B105" s="474" t="n">
         <v>8235.099999999999</v>
       </c>
-      <c r="C104" s="399">
+      <c r="C105" s="399">
         <f>(B101*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D104" s="399">
+      <c r="D105" s="399">
         <f>(B101*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="334" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="334" t="inlineStr">
         <is>
           <t>May 18 - May 24</t>
         </is>
       </c>
-      <c r="B105" s="471" t="n">
+      <c r="B106" s="471" t="n">
         <v>9724.809999999999</v>
       </c>
-      <c r="C105" s="399" t="n">
+      <c r="C106" s="399" t="n">
         <v>659.3421179999998</v>
       </c>
-      <c r="D105" s="399" t="n">
+      <c r="D106" s="399" t="n">
         <v>219.780706</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="353" t="n"/>
-      <c r="B106" s="474" t="n"/>
-      <c r="C106" s="399" t="n"/>
-      <c r="D106" s="399" t="n"/>
-    </row>
     <row r="107">
-      <c r="A107" s="334" t="n"/>
-      <c r="B107" s="471" t="n"/>
+      <c r="A107" s="353" t="n"/>
+      <c r="B107" s="474" t="n"/>
       <c r="C107" s="399" t="n"/>
       <c r="D107" s="399" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="353" t="n"/>
-      <c r="B108" s="474" t="n"/>
+      <c r="A108" s="334" t="n"/>
+      <c r="B108" s="471" t="n"/>
       <c r="C108" s="399" t="n"/>
       <c r="D108" s="399" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="353" t="n"/>
+      <c r="B109" s="474" t="n"/>
+      <c r="C109" s="399" t="n"/>
+      <c r="D109" s="399" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -52589,7 +53013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC107"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="39.6640625" customWidth="1" min="1" max="1"/>
@@ -57376,16 +57800,32 @@
       <c r="AC88" s="402" t="n"/>
     </row>
     <row r="89" ht="27.6" customHeight="1">
-      <c r="A89" s="353" t="n"/>
+      <c r="A89" s="353" t="inlineStr">
+        <is>
+          <t>May 25 - May 31</t>
+        </is>
+      </c>
       <c r="B89" s="545" t="n"/>
       <c r="C89" s="398" t="n"/>
       <c r="D89" s="398" t="n"/>
-      <c r="E89" s="319" t="n"/>
-      <c r="F89" s="401" t="n"/>
-      <c r="G89" s="402" t="n"/>
-      <c r="H89" s="402" t="n"/>
-      <c r="I89" s="402" t="n"/>
-      <c r="J89" s="402" t="n"/>
+      <c r="E89" s="319" t="n">
+        <v>535</v>
+      </c>
+      <c r="F89" s="401" t="n">
+        <v>15783.72</v>
+      </c>
+      <c r="G89" s="402" t="n">
+        <v>4951.65</v>
+      </c>
+      <c r="H89" s="402" t="n">
+        <v>287.54</v>
+      </c>
+      <c r="I89" s="402" t="n">
+        <v>2308.83</v>
+      </c>
+      <c r="J89" s="402" t="n">
+        <v>8235.700000000001</v>
+      </c>
       <c r="K89" s="405" t="n"/>
       <c r="L89" s="405" t="n"/>
       <c r="M89" s="402" t="n"/>
@@ -57407,54 +57847,47 @@
       <c r="AC89" s="402" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="45" t="inlineStr">
+      <c r="A90" s="353" t="n"/>
+      <c r="B90" s="545" t="n"/>
+      <c r="C90" s="398" t="n"/>
+      <c r="D90" s="398" t="n"/>
+      <c r="E90" s="319" t="n"/>
+      <c r="F90" s="401" t="n"/>
+      <c r="G90" s="402" t="n"/>
+      <c r="H90" s="402" t="n"/>
+      <c r="I90" s="402" t="n"/>
+      <c r="J90" s="402" t="n"/>
+      <c r="K90" s="405" t="n"/>
+      <c r="L90" s="405" t="n"/>
+      <c r="M90" s="402" t="n"/>
+      <c r="N90" s="402" t="n"/>
+      <c r="O90" s="402" t="n"/>
+      <c r="P90" s="402" t="n"/>
+      <c r="Q90" s="448" t="n"/>
+      <c r="R90" s="448" t="n"/>
+      <c r="S90" s="402" t="n"/>
+      <c r="T90" s="402" t="n"/>
+      <c r="U90" s="402" t="n"/>
+      <c r="V90" s="402" t="n"/>
+      <c r="W90" s="402" t="n"/>
+      <c r="X90" s="402" t="n"/>
+      <c r="Y90" s="402" t="n"/>
+      <c r="Z90" s="402" t="n"/>
+      <c r="AA90" s="402" t="n"/>
+      <c r="AB90" s="402" t="n"/>
+      <c r="AC90" s="402" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="45" t="inlineStr">
         <is>
           <t>PK Queen St.</t>
         </is>
       </c>
-      <c r="B90" s="358" t="n"/>
-      <c r="C90" s="358" t="n"/>
-      <c r="D90" s="355" t="n"/>
-      <c r="E90" s="45" t="n"/>
-      <c r="F90" s="45" t="n"/>
-      <c r="G90" s="56" t="n"/>
-      <c r="H90" s="56" t="n"/>
-      <c r="I90" s="56" t="n"/>
-      <c r="J90" s="56" t="n"/>
-      <c r="K90" s="56" t="n"/>
-      <c r="L90" s="56" t="n"/>
-      <c r="M90" s="56" t="n"/>
-      <c r="N90" s="56" t="n"/>
-      <c r="O90" s="56" t="n"/>
-      <c r="P90" s="56" t="n"/>
-      <c r="Q90" s="56" t="n"/>
-      <c r="R90" s="56" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="30" t="inlineStr">
-        <is>
-          <t>Statement For Selected Period</t>
-        </is>
-      </c>
-      <c r="B91" s="30" t="inlineStr">
-        <is>
-          <t>Total Revenue (Net Sales)</t>
-        </is>
-      </c>
-      <c r="C91" s="30" t="inlineStr">
-        <is>
-          <t>Royalties
-(6%) +HST</t>
-        </is>
-      </c>
-      <c r="D91" s="30" t="inlineStr">
-        <is>
-          <t>Marketing
-(2%) +HST</t>
-        </is>
-      </c>
-      <c r="E91" s="30" t="n"/>
-      <c r="F91" s="30" t="n"/>
+      <c r="B91" s="358" t="n"/>
+      <c r="C91" s="358" t="n"/>
+      <c r="D91" s="355" t="n"/>
+      <c r="E91" s="45" t="n"/>
+      <c r="F91" s="45" t="n"/>
       <c r="G91" s="56" t="n"/>
       <c r="H91" s="56" t="n"/>
       <c r="I91" s="56" t="n"/>
@@ -57469,24 +57902,30 @@
       <c r="R91" s="56" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>Mar 09 - Mar 15 2026</t>
-        </is>
-      </c>
-      <c r="B92" s="389" t="n">
-        <v>14325.5</v>
-      </c>
-      <c r="C92" s="398">
-        <f>(B87*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D92" s="398">
-        <f>(B87*0.02)*1.13</f>
-        <v/>
-      </c>
-      <c r="E92" s="56" t="n"/>
-      <c r="F92" s="56" t="n"/>
+      <c r="A92" s="30" t="inlineStr">
+        <is>
+          <t>Statement For Selected Period</t>
+        </is>
+      </c>
+      <c r="B92" s="30" t="inlineStr">
+        <is>
+          <t>Total Revenue (Net Sales)</t>
+        </is>
+      </c>
+      <c r="C92" s="30" t="inlineStr">
+        <is>
+          <t>Royalties
+(6%) +HST</t>
+        </is>
+      </c>
+      <c r="D92" s="30" t="inlineStr">
+        <is>
+          <t>Marketing
+(2%) +HST</t>
+        </is>
+      </c>
+      <c r="E92" s="30" t="n"/>
+      <c r="F92" s="30" t="n"/>
       <c r="G92" s="56" t="n"/>
       <c r="H92" s="56" t="n"/>
       <c r="I92" s="56" t="n"/>
@@ -57503,18 +57942,18 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>Mar 16 - Mar 22 2026</t>
+          <t>Mar 09 - Mar 15 2026</t>
         </is>
       </c>
       <c r="B93" s="389" t="n">
-        <v>15858.82</v>
+        <v>14325.5</v>
       </c>
       <c r="C93" s="398">
-        <f>(B88*0.06)*1.13</f>
+        <f>(B87*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D93" s="398">
-        <f>(B88*0.02)*1.13</f>
+        <f>(B87*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E93" s="56" t="n"/>
@@ -57535,18 +57974,18 @@
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>Mar 23 - Mar 29 2026</t>
+          <t>Mar 16 - Mar 22 2026</t>
         </is>
       </c>
       <c r="B94" s="389" t="n">
-        <v>17564.11</v>
+        <v>15858.82</v>
       </c>
       <c r="C94" s="398">
-        <f>(B89*0.06)*1.13</f>
+        <f>(B88*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D94" s="398">
-        <f>(B89*0.02)*1.13</f>
+        <f>(B88*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E94" s="56" t="n"/>
@@ -57567,18 +58006,18 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>Mar 30 - Apr 05 2026</t>
+          <t>Mar 23 - Mar 29 2026</t>
         </is>
       </c>
       <c r="B95" s="389" t="n">
-        <v>16208.28</v>
+        <v>17564.11</v>
       </c>
       <c r="C95" s="398">
-        <f>(B90*0.06)*1.13</f>
+        <f>(B89*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D95" s="398">
-        <f>(B90*0.02)*1.13</f>
+        <f>(B89*0.02)*1.13</f>
         <v/>
       </c>
       <c r="E95" s="56" t="n"/>
@@ -57597,158 +58036,190 @@
       <c r="R95" s="56" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>Mar 30 - Apr 05 2026</t>
+        </is>
+      </c>
+      <c r="B96" s="389" t="n">
+        <v>16208.28</v>
+      </c>
+      <c r="C96" s="398">
+        <f>(B90*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D96" s="398">
+        <f>(B90*0.02)*1.13</f>
+        <v/>
+      </c>
+      <c r="E96" s="56" t="n"/>
+      <c r="F96" s="56" t="n"/>
+      <c r="G96" s="56" t="n"/>
+      <c r="H96" s="56" t="n"/>
+      <c r="I96" s="56" t="n"/>
+      <c r="J96" s="56" t="n"/>
+      <c r="K96" s="56" t="n"/>
+      <c r="L96" s="56" t="n"/>
+      <c r="M96" s="56" t="n"/>
+      <c r="N96" s="56" t="n"/>
+      <c r="O96" s="56" t="n"/>
+      <c r="P96" s="56" t="n"/>
+      <c r="Q96" s="56" t="n"/>
+      <c r="R96" s="56" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Apr 06 - Apr 12</t>
         </is>
       </c>
-      <c r="B96" s="389" t="n">
+      <c r="B97" s="389" t="n">
         <v>15776.96</v>
       </c>
-      <c r="C96" s="398">
+      <c r="C97" s="398">
         <f>(B91*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D96" s="398">
+      <c r="D97" s="398">
         <f>(B91*0.02)*1.13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t>Apr 13 - Apr 19</t>
-        </is>
-      </c>
-      <c r="B97" s="389" t="n">
-        <v>15478.96</v>
-      </c>
-      <c r="C97" s="398">
-        <f>(B92*0.06)*1.13</f>
-        <v/>
-      </c>
-      <c r="D97" s="398">
-        <f>(B92*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>Apr 20 - Apr 26</t>
+          <t>Apr 13 - Apr 19</t>
         </is>
       </c>
       <c r="B98" s="389" t="n">
-        <v>16027.28</v>
+        <v>15478.96</v>
       </c>
       <c r="C98" s="398">
-        <f>(B93*0.06)*1.13</f>
+        <f>(B92*0.06)*1.13</f>
         <v/>
       </c>
       <c r="D98" s="398">
-        <f>(B93*0.02)*1.13</f>
+        <f>(B92*0.02)*1.13</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
+          <t>Apr 20 - Apr 26</t>
+        </is>
+      </c>
+      <c r="B99" s="389" t="n">
+        <v>16027.28</v>
+      </c>
+      <c r="C99" s="398">
+        <f>(B93*0.06)*1.13</f>
+        <v/>
+      </c>
+      <c r="D99" s="398">
+        <f>(B93*0.02)*1.13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
           <t>Apr 27 - May 03</t>
         </is>
       </c>
-      <c r="B99" s="389" t="n">
+      <c r="B100" s="389" t="n">
         <v>16047.12</v>
       </c>
-      <c r="C99" s="398">
+      <c r="C100" s="398">
         <f>(B95*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D99" s="398">
+      <c r="D100" s="398">
         <f>(B95*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>May 4 - May 10</t>
         </is>
       </c>
-      <c r="B100" s="389" t="n">
+      <c r="B101" s="389" t="n">
         <v>16939.43</v>
       </c>
-      <c r="C100" s="398">
+      <c r="C101" s="398">
         <f>(B96*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D100" s="398">
+      <c r="D101" s="398">
         <f>(B96*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="11" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>May 11 - May 17</t>
         </is>
       </c>
-      <c r="B101" s="389" t="n">
+      <c r="B102" s="389" t="n">
         <v>16229.03</v>
       </c>
-      <c r="C101" s="398">
+      <c r="C102" s="398">
         <f>(B98*0.06)*1.13</f>
         <v/>
       </c>
-      <c r="D101" s="398">
+      <c r="D102" s="398">
         <f>(B98*0.02)*1.13</f>
         <v/>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>May 18 - May 24</t>
         </is>
       </c>
-      <c r="B102" s="389" t="n">
+      <c r="B103" s="389" t="n">
         <v>15162.52</v>
       </c>
-      <c r="C102" s="398" t="n">
+      <c r="C103" s="398" t="n">
         <v>1028.018856</v>
       </c>
-      <c r="D102" s="398" t="n">
+      <c r="D103" s="398" t="n">
         <v>342.6729519999999</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="11" t="n"/>
-      <c r="B103" s="389" t="n"/>
-      <c r="C103" s="398" t="n"/>
-      <c r="D103" s="398" t="n"/>
-    </row>
     <row r="104">
-      <c r="A104" s="2" t="n"/>
+      <c r="A104" s="11" t="n"/>
       <c r="B104" s="389" t="n"/>
       <c r="C104" s="398" t="n"/>
       <c r="D104" s="398" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="n"/>
+      <c r="A105" s="2" t="n"/>
       <c r="B105" s="389" t="n"/>
       <c r="C105" s="398" t="n"/>
       <c r="D105" s="398" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n"/>
+      <c r="A106" s="11" t="n"/>
       <c r="B106" s="389" t="n"/>
       <c r="C106" s="398" t="n"/>
       <c r="D106" s="398" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="n"/>
+      <c r="A107" s="2" t="n"/>
       <c r="B107" s="389" t="n"/>
       <c r="C107" s="398" t="n"/>
       <c r="D107" s="398" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="n"/>
+      <c r="B108" s="389" t="n"/>
+      <c r="C108" s="398" t="n"/>
+      <c r="D108" s="398" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
